--- a/posts/assurance_maladie/data/salaires_ofs.xlsx
+++ b/posts/assurance_maladie/data/salaires_ofs.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\celalguney\posts\assurance_maladie\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4FBC79C-9D7A-4841-9EA0-B66657C543D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9751C23D-6B8F-49E9-9D04-24C4FF341D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="1388" windowWidth="21600" windowHeight="14040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="27390" windowHeight="15563" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2010-2024" sheetId="4" r:id="rId1"/>
     <sheet name="1976-2009" sheetId="2" r:id="rId2"/>
     <sheet name="1942-1975" sheetId="1" r:id="rId3"/>
-    <sheet name="Feuil1" sheetId="5" r:id="rId4"/>
+    <sheet name="Graphique1" sheetId="6" r:id="rId4"/>
+    <sheet name="Feuil1" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2010-2024'!$A$1:$O$32</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="131">
   <si>
     <t xml:space="preserve"> Année</t>
   </si>
@@ -464,6 +465,42 @@
   </si>
   <si>
     <t>indice_salaire_nominal</t>
+  </si>
+  <si>
+    <t>cout_prestation_sante_hab</t>
+  </si>
+  <si>
+    <t>cout_prest_sante</t>
+  </si>
+  <si>
+    <t>cout_pres_sante_pib</t>
+  </si>
+  <si>
+    <t>ipam_total</t>
+  </si>
+  <si>
+    <t>ipam_base</t>
+  </si>
+  <si>
+    <t>ipam_compl</t>
+  </si>
+  <si>
+    <t>Influence de l'évolution des primes sur la croissance de revenu disponible (subventions incl.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>salaire_reel100</t>
+  </si>
+  <si>
+    <t>salaire_nominal100</t>
+  </si>
+  <si>
+    <t>pib_reel_chain2020</t>
+  </si>
+  <si>
+    <t>pib_reel_100</t>
   </si>
 </sst>
 </file>
@@ -996,6 +1033,50 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="6" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="8" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1060,50 +1141,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="6" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="8" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1125,6 +1162,1488 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Indice_salaire_reel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Feuil1!$A$59:$A$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$K$59:$K$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99.642857142857139</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>101.42857142857142</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102.49999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>103.21428571428572</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>103.21428571428572</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>103.21428571428572</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>103.21428571428572</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>104.28571428571429</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>103.57142857142858</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>106.42857142857143</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>106.42857142857143</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>107.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>108.92857142857142</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>110.00000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>111.07142857142858</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>112.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>113.92857142857142</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>113.57142857142857</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>113.21428571428571</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>113.92857142857142</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115.71428571428572</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>114.64285714285714</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>112.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>112.14285714285714</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>112.85714285714286</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B5E9-4856-8983-105A5C3F17A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ipam_total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Feuil1!$A$59:$A$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$G$2:$G$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>104.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>110.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>127.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>136.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>141.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>143.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>142.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>144.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>156.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>165.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>168.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>170.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>173.3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>178.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>185.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>192.83425255256284</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>194.4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>194.8</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>195.3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>194.4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>213.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B5E9-4856-8983-105A5C3F17A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>salaire_nominal100</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$L$59:$L$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>101.28998968008256</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>103.76676986584108</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>105.62435500515997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>107.12074303405572</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>108.10113519091846</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>109.13312693498452</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>110.42311661506707</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>112.22910216718267</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>114.49948400412796</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>116.92466460268318</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>117.85345717234262</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>118.98864809081526</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>120.02063983488131</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>120.89783281733746</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>121.82662538699691</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>122.29102167182661</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>123.11661506707947</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>123.58101135190918</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>124.20020639834881</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>125.33539731682146</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>126.36738906088752</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>126.16099071207429</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>127.34778121775025</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>129.51496388028895</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>131.83694530443756</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B5E9-4856-8983-105A5C3F17A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>pib_reel_100</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$N$59:$N$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>103.63321686150913</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>105.28326257599619</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>105.68377085756065</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105.38339384992861</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>108.10958737343152</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>111.30107417133748</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>115.90261962745933</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120.51924551296314</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>123.57030626059154</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>121.17933267189468</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>125.1305433118447</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>126.89195668542077</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>128.31839471287014</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>130.67447943455534</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>133.99808482718694</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>135.94709132467457</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>138.5458437723818</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>140.51367429793868</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>145.18917197516453</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>146.80849860522659</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>143.49758821527635</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>152.36032699132244</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>157.7452024689922</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>159.04748513933313</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>161.25877584771806</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B5E9-4856-8983-105A5C3F17A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1829569023"/>
+        <c:axId val="1829569503"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1829569023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1829569503"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1829569503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="99"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1829569023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15439035536331291"/>
+          <c:y val="0.14080175259618349"/>
+          <c:w val="0.15657552704704558"/>
+          <c:h val="0.25436206451418841"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{4E45FC4C-E1B4-4E57-B1FB-6D795D392E68}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1306,6 +2825,39 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9296715" cy="6073171"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A280EDD-A3BB-C4D9-62EF-D4919A146EC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1683,62 +3235,62 @@
       <c r="N4" s="81"/>
     </row>
     <row r="5" spans="1:18" s="27" customFormat="1" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="114"/>
-      <c r="B5" s="105" t="s">
+      <c r="A5" s="132"/>
+      <c r="B5" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="105" t="s">
+      <c r="C5" s="124"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="116" t="s">
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="I5" s="105" t="s">
+      <c r="I5" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="J5" s="106"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="105" t="s">
+      <c r="J5" s="124"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="M5" s="106"/>
-      <c r="N5" s="107"/>
+      <c r="M5" s="124"/>
+      <c r="N5" s="125"/>
     </row>
     <row r="6" spans="1:18" s="30" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="115"/>
-      <c r="B6" s="108"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="109"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="109"/>
-      <c r="N6" s="110"/>
+      <c r="A6" s="133"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="126"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="126"/>
+      <c r="M6" s="127"/>
+      <c r="N6" s="128"/>
     </row>
     <row r="7" spans="1:18" s="27" customFormat="1" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="115"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="113"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="113"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="113"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="131"/>
     </row>
     <row r="8" spans="1:18" s="27" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="83" t="s">
@@ -1762,7 +3314,7 @@
       <c r="G8" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="118"/>
+      <c r="H8" s="136"/>
       <c r="I8" s="104" t="s">
         <v>5</v>
       </c>
@@ -9061,61 +10613,61 @@
     </row>
     <row r="7" spans="1:14" s="27" customFormat="1" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25"/>
-      <c r="B7" s="119" t="s">
+      <c r="B7" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="120"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="119" t="s">
+      <c r="C7" s="138"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="128" t="s">
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="119" t="s">
+      <c r="I7" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="120"/>
-      <c r="K7" s="121"/>
-      <c r="L7" s="119" t="s">
+      <c r="J7" s="138"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="M7" s="120"/>
-      <c r="N7" s="120"/>
+      <c r="M7" s="138"/>
+      <c r="N7" s="138"/>
     </row>
     <row r="8" spans="1:14" s="30" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="29"/>
-      <c r="B8" s="122"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="123"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="123"/>
-      <c r="N8" s="123"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="142"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="141"/>
     </row>
     <row r="9" spans="1:14" s="27" customFormat="1" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
+      <c r="B9" s="143"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="143"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="145"/>
+      <c r="L9" s="143"/>
+      <c r="M9" s="144"/>
+      <c r="N9" s="144"/>
     </row>
     <row r="10" spans="1:14" s="27" customFormat="1" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25"/>
@@ -9125,7 +10677,7 @@
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
-      <c r="H10" s="117"/>
+      <c r="H10" s="135"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
@@ -9155,7 +10707,7 @@
       <c r="G11" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="117"/>
+      <c r="H11" s="135"/>
       <c r="I11" s="16" t="s">
         <v>5</v>
       </c>
@@ -9183,7 +10735,7 @@
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
-      <c r="H12" s="118"/>
+      <c r="H12" s="136"/>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
@@ -17220,7 +18772,7 @@
     <col min="1" max="1" width="5.53125" style="19" customWidth="1"/>
     <col min="2" max="7" width="6.53125" style="19" customWidth="1"/>
     <col min="8" max="8" width="11.19921875" style="19" customWidth="1"/>
-    <col min="9" max="9" width="6.53125" style="146" customWidth="1"/>
+    <col min="9" max="9" width="6.53125" style="122" customWidth="1"/>
     <col min="10" max="14" width="6.53125" style="19" customWidth="1"/>
     <col min="15" max="16384" width="11.46484375" style="56"/>
   </cols>
@@ -17236,7 +18788,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="129"/>
+      <c r="I1" s="105"/>
       <c r="J1" s="21"/>
       <c r="K1" s="21"/>
       <c r="L1" s="21"/>
@@ -17252,7 +18804,7 @@
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="130"/>
+      <c r="I2" s="106"/>
       <c r="J2" s="22"/>
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
@@ -17268,7 +18820,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="4"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="131"/>
+      <c r="I3" s="107"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -17288,7 +18840,7 @@
       <c r="H4" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="132" t="s">
+      <c r="I4" s="108" t="s">
         <v>76</v>
       </c>
       <c r="J4" s="5"/>
@@ -17308,7 +18860,7 @@
       <c r="H5" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I5" s="132"/>
+      <c r="I5" s="108"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -17324,7 +18876,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="13"/>
       <c r="H6" s="11"/>
-      <c r="I6" s="133"/>
+      <c r="I6" s="109"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
@@ -17333,61 +18885,61 @@
     </row>
     <row r="7" spans="1:14" s="27" customFormat="1" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25"/>
-      <c r="B7" s="119" t="s">
+      <c r="B7" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="120"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="119" t="s">
+      <c r="C7" s="138"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="128" t="s">
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="119" t="s">
+      <c r="I7" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="120"/>
-      <c r="K7" s="121"/>
-      <c r="L7" s="119" t="s">
+      <c r="J7" s="138"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="M7" s="120"/>
-      <c r="N7" s="120"/>
+      <c r="M7" s="138"/>
+      <c r="N7" s="138"/>
     </row>
     <row r="8" spans="1:14" s="30" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="29"/>
-      <c r="B8" s="122"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="123"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="123"/>
-      <c r="N8" s="123"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="142"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="141"/>
     </row>
     <row r="9" spans="1:14" s="27" customFormat="1" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
+      <c r="B9" s="143"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="143"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="145"/>
+      <c r="L9" s="143"/>
+      <c r="M9" s="144"/>
+      <c r="N9" s="144"/>
     </row>
     <row r="10" spans="1:14" s="27" customFormat="1" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25"/>
@@ -17397,8 +18949,8 @@
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="134"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="110"/>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
       <c r="L10" s="14"/>
@@ -17427,8 +18979,8 @@
       <c r="G11" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="117"/>
-      <c r="I11" s="135" t="s">
+      <c r="H11" s="135"/>
+      <c r="I11" s="111" t="s">
         <v>5</v>
       </c>
       <c r="J11" s="15" t="s">
@@ -17455,8 +19007,8 @@
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="112"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
@@ -17472,7 +19024,7 @@
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
       <c r="H13" s="31"/>
-      <c r="I13" s="137"/>
+      <c r="I13" s="113"/>
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
       <c r="L13" s="31"/>
@@ -17496,7 +19048,7 @@
       <c r="F14" s="35"/>
       <c r="G14" s="35"/>
       <c r="H14" s="36"/>
-      <c r="I14" s="138">
+      <c r="I14" s="114">
         <v>100</v>
       </c>
       <c r="J14" s="33">
@@ -17530,7 +19082,7 @@
       <c r="H15" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="I15" s="138" t="s">
+      <c r="I15" s="114" t="s">
         <v>6</v>
       </c>
       <c r="J15" s="39" t="s">
@@ -17562,7 +19114,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
-      <c r="I16" s="138" t="s">
+      <c r="I16" s="114" t="s">
         <v>6</v>
       </c>
       <c r="J16" s="33" t="s">
@@ -17592,7 +19144,7 @@
       <c r="F17" s="48"/>
       <c r="G17" s="48"/>
       <c r="H17" s="49"/>
-      <c r="I17" s="139">
+      <c r="I17" s="115">
         <v>87</v>
       </c>
       <c r="J17" s="46">
@@ -17630,7 +19182,7 @@
       <c r="H18" s="36">
         <v>3.8</v>
       </c>
-      <c r="I18" s="139">
+      <c r="I18" s="115">
         <v>90</v>
       </c>
       <c r="J18" s="50">
@@ -17674,7 +19226,7 @@
       <c r="H19" s="49">
         <v>1.6</v>
       </c>
-      <c r="I19" s="139">
+      <c r="I19" s="115">
         <v>94</v>
       </c>
       <c r="J19" s="46">
@@ -17718,7 +19270,7 @@
       <c r="H20" s="36">
         <v>0</v>
       </c>
-      <c r="I20" s="139">
+      <c r="I20" s="115">
         <v>101</v>
       </c>
       <c r="J20" s="50">
@@ -17762,7 +19314,7 @@
       <c r="H21" s="49">
         <v>1.5</v>
       </c>
-      <c r="I21" s="138">
+      <c r="I21" s="114">
         <v>110</v>
       </c>
       <c r="J21" s="46">
@@ -17806,7 +19358,7 @@
       <c r="H22" s="36">
         <v>5.3</v>
       </c>
-      <c r="I22" s="139">
+      <c r="I22" s="115">
         <v>113</v>
       </c>
       <c r="J22" s="50">
@@ -17850,7 +19402,7 @@
       <c r="H23" s="49">
         <v>0.2</v>
       </c>
-      <c r="I23" s="138">
+      <c r="I23" s="114">
         <v>119</v>
       </c>
       <c r="J23" s="46">
@@ -17894,7 +19446,7 @@
       <c r="H24" s="36">
         <v>-0.9</v>
       </c>
-      <c r="I24" s="139">
+      <c r="I24" s="115">
         <v>121</v>
       </c>
       <c r="J24" s="50">
@@ -17938,7 +19490,7 @@
       <c r="H25" s="49">
         <v>-0.5</v>
       </c>
-      <c r="I25" s="138">
+      <c r="I25" s="114">
         <v>123</v>
       </c>
       <c r="J25" s="46">
@@ -17982,7 +19534,7 @@
       <c r="H26" s="36">
         <v>5.7</v>
       </c>
-      <c r="I26" s="139">
+      <c r="I26" s="115">
         <v>121</v>
       </c>
       <c r="J26" s="50">
@@ -18026,7 +19578,7 @@
       <c r="H27" s="49">
         <v>0.7</v>
       </c>
-      <c r="I27" s="138">
+      <c r="I27" s="114">
         <v>124</v>
       </c>
       <c r="J27" s="46">
@@ -18070,7 +19622,7 @@
       <c r="H28" s="36">
         <v>-0.3</v>
       </c>
-      <c r="I28" s="139">
+      <c r="I28" s="115">
         <v>126</v>
       </c>
       <c r="J28" s="50">
@@ -18114,7 +19666,7 @@
       <c r="H29" s="49">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I29" s="138">
+      <c r="I29" s="114">
         <v>126</v>
       </c>
       <c r="J29" s="46">
@@ -18158,7 +19710,7 @@
       <c r="H30" s="36">
         <v>0.7</v>
       </c>
-      <c r="I30" s="139">
+      <c r="I30" s="115">
         <v>129</v>
       </c>
       <c r="J30" s="50">
@@ -18202,7 +19754,7 @@
       <c r="H31" s="49">
         <v>1.9</v>
       </c>
-      <c r="I31" s="138">
+      <c r="I31" s="114">
         <v>132</v>
       </c>
       <c r="J31" s="46">
@@ -18246,7 +19798,7 @@
       <c r="H32" s="36">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I32" s="139">
+      <c r="I32" s="115">
         <v>135</v>
       </c>
       <c r="J32" s="50">
@@ -18290,7 +19842,7 @@
       <c r="H33" s="49">
         <v>1.3</v>
       </c>
-      <c r="I33" s="139">
+      <c r="I33" s="115">
         <v>138</v>
       </c>
       <c r="J33" s="46">
@@ -18334,7 +19886,7 @@
       <c r="H34" s="36">
         <v>-0.8</v>
       </c>
-      <c r="I34" s="139">
+      <c r="I34" s="115">
         <v>143</v>
       </c>
       <c r="J34" s="50">
@@ -18378,7 +19930,7 @@
       <c r="H35" s="49">
         <v>1.9</v>
       </c>
-      <c r="I35" s="139">
+      <c r="I35" s="115">
         <v>147</v>
       </c>
       <c r="J35" s="46">
@@ -18422,7 +19974,7 @@
       <c r="H36" s="36">
         <v>1.9</v>
       </c>
-      <c r="I36" s="139">
+      <c r="I36" s="115">
         <v>153</v>
       </c>
       <c r="J36" s="50">
@@ -18466,7 +20018,7 @@
       <c r="H37" s="49">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I37" s="139">
+      <c r="I37" s="115">
         <v>158</v>
       </c>
       <c r="J37" s="46">
@@ -18510,7 +20062,7 @@
       <c r="H38" s="36">
         <v>3.8</v>
       </c>
-      <c r="I38" s="139">
+      <c r="I38" s="115">
         <v>164</v>
       </c>
       <c r="J38" s="50">
@@ -18554,7 +20106,7 @@
       <c r="H39" s="49">
         <v>2.8</v>
       </c>
-      <c r="I39" s="139">
+      <c r="I39" s="115">
         <v>171</v>
       </c>
       <c r="J39" s="46">
@@ -18598,7 +20150,7 @@
       <c r="H40" s="36">
         <v>4</v>
       </c>
-      <c r="I40" s="139">
+      <c r="I40" s="115">
         <v>176</v>
       </c>
       <c r="J40" s="50">
@@ -18642,7 +20194,7 @@
       <c r="H41" s="49">
         <v>4</v>
       </c>
-      <c r="I41" s="139">
+      <c r="I41" s="115">
         <v>182</v>
       </c>
       <c r="J41" s="46">
@@ -18686,7 +20238,7 @@
       <c r="H42" s="36">
         <v>4</v>
       </c>
-      <c r="I42" s="139">
+      <c r="I42" s="115">
         <v>186</v>
       </c>
       <c r="J42" s="50">
@@ -18730,7 +20282,7 @@
       <c r="H43" s="49">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I43" s="139">
+      <c r="I43" s="115">
         <v>191</v>
       </c>
       <c r="J43" s="46">
@@ -18774,7 +20326,7 @@
       <c r="H44" s="36">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I44" s="139">
+      <c r="I44" s="115">
         <v>198</v>
       </c>
       <c r="J44" s="50">
@@ -18818,7 +20370,7 @@
       <c r="H45" s="49">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I45" s="139">
+      <c r="I45" s="115">
         <v>207</v>
       </c>
       <c r="J45" s="46">
@@ -18862,7 +20414,7 @@
       <c r="H46" s="36">
         <v>6.6</v>
       </c>
-      <c r="I46" s="139">
+      <c r="I46" s="115">
         <v>218</v>
       </c>
       <c r="J46" s="50">
@@ -18906,7 +20458,7 @@
       <c r="H47" s="49">
         <v>7.3</v>
       </c>
-      <c r="I47" s="139">
+      <c r="I47" s="115">
         <v>226</v>
       </c>
       <c r="J47" s="46">
@@ -18950,7 +20502,7 @@
       <c r="H48" s="36">
         <v>9.5</v>
       </c>
-      <c r="I48" s="139">
+      <c r="I48" s="115">
         <v>231</v>
       </c>
       <c r="J48" s="50">
@@ -18994,7 +20546,7 @@
       <c r="H49" s="49">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I49" s="139">
+      <c r="I49" s="115">
         <v>236</v>
       </c>
       <c r="J49" s="46">
@@ -19038,7 +20590,7 @@
       <c r="H50" s="36">
         <v>4.8</v>
       </c>
-      <c r="I50" s="139">
+      <c r="I50" s="115">
         <v>242</v>
       </c>
       <c r="J50" s="50">
@@ -19066,7 +20618,7 @@
       <c r="F51" s="65"/>
       <c r="G51" s="65"/>
       <c r="H51" s="65"/>
-      <c r="I51" s="140"/>
+      <c r="I51" s="116"/>
       <c r="J51" s="65"/>
       <c r="K51" s="65"/>
       <c r="L51" s="65"/>
@@ -19240,7 +20792,7 @@
       <c r="F52" s="55"/>
       <c r="G52" s="55"/>
       <c r="H52" s="55"/>
-      <c r="I52" s="141"/>
+      <c r="I52" s="117"/>
       <c r="J52" s="55"/>
       <c r="K52" s="55"/>
       <c r="L52" s="55"/>
@@ -19258,7 +20810,7 @@
       <c r="F53" s="18"/>
       <c r="G53" s="18"/>
       <c r="H53" s="18"/>
-      <c r="I53" s="142"/>
+      <c r="I53" s="118"/>
       <c r="J53" s="18"/>
       <c r="K53" s="18"/>
       <c r="L53" s="18"/>
@@ -19276,7 +20828,7 @@
       <c r="F54" s="18"/>
       <c r="G54" s="18"/>
       <c r="H54" s="18"/>
-      <c r="I54" s="142"/>
+      <c r="I54" s="118"/>
       <c r="J54" s="18"/>
       <c r="K54" s="18"/>
       <c r="L54" s="18"/>
@@ -19294,7 +20846,7 @@
       <c r="F55" s="18"/>
       <c r="G55" s="18"/>
       <c r="H55" s="18"/>
-      <c r="I55" s="142"/>
+      <c r="I55" s="118"/>
       <c r="J55" s="18"/>
       <c r="K55" s="18"/>
       <c r="L55" s="18"/>
@@ -19312,7 +20864,7 @@
       <c r="F56" s="18"/>
       <c r="G56" s="18"/>
       <c r="H56" s="18"/>
-      <c r="I56" s="142"/>
+      <c r="I56" s="118"/>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
       <c r="L56" s="18"/>
@@ -19320,13 +20872,13 @@
       <c r="N56" s="18"/>
     </row>
     <row r="57" spans="1:172" s="58" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="I57" s="143"/>
+      <c r="I57" s="119"/>
     </row>
     <row r="58" spans="1:172" s="58" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="I58" s="143"/>
+      <c r="I58" s="119"/>
     </row>
     <row r="59" spans="1:172" x14ac:dyDescent="0.3">
       <c r="A59" s="67" t="s">
@@ -19339,7 +20891,7 @@
       <c r="F59" s="67"/>
       <c r="G59" s="67"/>
       <c r="H59" s="67"/>
-      <c r="I59" s="144"/>
+      <c r="I59" s="120"/>
       <c r="J59" s="67"/>
       <c r="K59" s="57"/>
       <c r="L59" s="57"/>
@@ -19357,18 +20909,18 @@
       <c r="F60" s="67"/>
       <c r="G60" s="67"/>
       <c r="H60" s="67"/>
-      <c r="I60" s="144"/>
+      <c r="I60" s="120"/>
       <c r="J60" s="67"/>
     </row>
     <row r="61" spans="1:172" s="58" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="I61" s="143"/>
+      <c r="I61" s="119"/>
     </row>
     <row r="62" spans="1:172" s="58" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="I62" s="143"/>
+      <c r="I62" s="119"/>
     </row>
     <row r="63" spans="1:172" s="58" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="59"/>
-      <c r="I63" s="143"/>
+      <c r="I63" s="119"/>
     </row>
     <row r="64" spans="1:172" x14ac:dyDescent="0.3">
       <c r="A64" s="54"/>
@@ -19379,7 +20931,7 @@
       <c r="F64" s="54"/>
       <c r="G64" s="54"/>
       <c r="H64" s="54"/>
-      <c r="I64" s="145"/>
+      <c r="I64" s="121"/>
       <c r="J64" s="54"/>
       <c r="K64" s="54"/>
       <c r="L64" s="54"/>
@@ -19395,7 +20947,7 @@
       <c r="F65" s="54"/>
       <c r="G65" s="54"/>
       <c r="H65" s="54"/>
-      <c r="I65" s="145"/>
+      <c r="I65" s="121"/>
       <c r="J65" s="54"/>
       <c r="K65" s="54"/>
       <c r="L65" s="54"/>
@@ -19411,7 +20963,7 @@
       <c r="F66" s="54"/>
       <c r="G66" s="54"/>
       <c r="H66" s="54"/>
-      <c r="I66" s="145"/>
+      <c r="I66" s="121"/>
       <c r="J66" s="54"/>
       <c r="K66" s="54"/>
       <c r="L66" s="54"/>
@@ -19427,7 +20979,7 @@
       <c r="F67" s="54"/>
       <c r="G67" s="54"/>
       <c r="H67" s="54"/>
-      <c r="I67" s="145"/>
+      <c r="I67" s="121"/>
       <c r="J67" s="54"/>
       <c r="K67" s="54"/>
       <c r="L67" s="54"/>
@@ -19443,7 +20995,7 @@
       <c r="F68" s="54"/>
       <c r="G68" s="54"/>
       <c r="H68" s="54"/>
-      <c r="I68" s="145"/>
+      <c r="I68" s="121"/>
       <c r="J68" s="54"/>
       <c r="K68" s="54"/>
       <c r="L68" s="54"/>
@@ -19459,7 +21011,7 @@
       <c r="F69" s="54"/>
       <c r="G69" s="54"/>
       <c r="H69" s="54"/>
-      <c r="I69" s="145"/>
+      <c r="I69" s="121"/>
       <c r="J69" s="54"/>
       <c r="K69" s="54"/>
       <c r="L69" s="54"/>
@@ -19475,7 +21027,7 @@
       <c r="F70" s="54"/>
       <c r="G70" s="54"/>
       <c r="H70" s="54"/>
-      <c r="I70" s="145"/>
+      <c r="I70" s="121"/>
       <c r="J70" s="54"/>
       <c r="K70" s="54"/>
       <c r="L70" s="54"/>
@@ -19491,7 +21043,7 @@
       <c r="F71" s="54"/>
       <c r="G71" s="54"/>
       <c r="H71" s="54"/>
-      <c r="I71" s="145"/>
+      <c r="I71" s="121"/>
       <c r="J71" s="54"/>
       <c r="K71" s="54"/>
       <c r="L71" s="54"/>
@@ -19507,7 +21059,7 @@
       <c r="F72" s="54"/>
       <c r="G72" s="54"/>
       <c r="H72" s="54"/>
-      <c r="I72" s="145"/>
+      <c r="I72" s="121"/>
       <c r="J72" s="54"/>
       <c r="K72" s="54"/>
       <c r="L72" s="54"/>
@@ -19523,7 +21075,7 @@
       <c r="F73" s="54"/>
       <c r="G73" s="54"/>
       <c r="H73" s="54"/>
-      <c r="I73" s="145"/>
+      <c r="I73" s="121"/>
       <c r="J73" s="54"/>
       <c r="K73" s="54"/>
       <c r="L73" s="54"/>
@@ -19539,7 +21091,7 @@
       <c r="F74" s="54"/>
       <c r="G74" s="54"/>
       <c r="H74" s="54"/>
-      <c r="I74" s="145"/>
+      <c r="I74" s="121"/>
       <c r="J74" s="54"/>
       <c r="K74" s="54"/>
       <c r="L74" s="54"/>
@@ -19555,7 +21107,7 @@
       <c r="F75" s="54"/>
       <c r="G75" s="54"/>
       <c r="H75" s="54"/>
-      <c r="I75" s="145"/>
+      <c r="I75" s="121"/>
       <c r="J75" s="54"/>
       <c r="K75" s="54"/>
       <c r="L75" s="54"/>
@@ -19571,7 +21123,7 @@
       <c r="F76" s="54"/>
       <c r="G76" s="54"/>
       <c r="H76" s="54"/>
-      <c r="I76" s="145"/>
+      <c r="I76" s="121"/>
       <c r="J76" s="54"/>
       <c r="K76" s="54"/>
       <c r="L76" s="54"/>
@@ -19587,7 +21139,7 @@
       <c r="F77" s="54"/>
       <c r="G77" s="54"/>
       <c r="H77" s="54"/>
-      <c r="I77" s="145"/>
+      <c r="I77" s="121"/>
       <c r="J77" s="54"/>
       <c r="K77" s="54"/>
       <c r="L77" s="54"/>
@@ -19603,7 +21155,7 @@
       <c r="F78" s="54"/>
       <c r="G78" s="54"/>
       <c r="H78" s="54"/>
-      <c r="I78" s="145"/>
+      <c r="I78" s="121"/>
       <c r="J78" s="54"/>
       <c r="K78" s="54"/>
       <c r="L78" s="54"/>
@@ -19619,7 +21171,7 @@
       <c r="F79" s="54"/>
       <c r="G79" s="54"/>
       <c r="H79" s="54"/>
-      <c r="I79" s="145"/>
+      <c r="I79" s="121"/>
       <c r="J79" s="54"/>
       <c r="K79" s="54"/>
       <c r="L79" s="54"/>
@@ -19635,7 +21187,7 @@
       <c r="F80" s="54"/>
       <c r="G80" s="54"/>
       <c r="H80" s="54"/>
-      <c r="I80" s="145"/>
+      <c r="I80" s="121"/>
       <c r="J80" s="54"/>
       <c r="K80" s="54"/>
       <c r="L80" s="54"/>
@@ -19651,7 +21203,7 @@
       <c r="F81" s="54"/>
       <c r="G81" s="54"/>
       <c r="H81" s="54"/>
-      <c r="I81" s="145"/>
+      <c r="I81" s="121"/>
       <c r="J81" s="54"/>
       <c r="K81" s="54"/>
       <c r="L81" s="54"/>
@@ -19667,7 +21219,7 @@
       <c r="F82" s="54"/>
       <c r="G82" s="54"/>
       <c r="H82" s="54"/>
-      <c r="I82" s="145"/>
+      <c r="I82" s="121"/>
       <c r="J82" s="54"/>
       <c r="K82" s="54"/>
       <c r="L82" s="54"/>
@@ -19683,7 +21235,7 @@
       <c r="F83" s="54"/>
       <c r="G83" s="54"/>
       <c r="H83" s="54"/>
-      <c r="I83" s="145"/>
+      <c r="I83" s="121"/>
       <c r="J83" s="54"/>
       <c r="K83" s="54"/>
       <c r="L83" s="54"/>
@@ -19699,7 +21251,7 @@
       <c r="F84" s="54"/>
       <c r="G84" s="54"/>
       <c r="H84" s="54"/>
-      <c r="I84" s="145"/>
+      <c r="I84" s="121"/>
       <c r="J84" s="54"/>
       <c r="K84" s="54"/>
       <c r="L84" s="54"/>
@@ -19715,7 +21267,7 @@
       <c r="F85" s="54"/>
       <c r="G85" s="54"/>
       <c r="H85" s="54"/>
-      <c r="I85" s="145"/>
+      <c r="I85" s="121"/>
       <c r="J85" s="54"/>
       <c r="K85" s="54"/>
       <c r="L85" s="54"/>
@@ -19731,7 +21283,7 @@
       <c r="F86" s="54"/>
       <c r="G86" s="54"/>
       <c r="H86" s="54"/>
-      <c r="I86" s="145"/>
+      <c r="I86" s="121"/>
       <c r="J86" s="54"/>
       <c r="K86" s="54"/>
       <c r="L86" s="54"/>
@@ -19747,7 +21299,7 @@
       <c r="F87" s="54"/>
       <c r="G87" s="54"/>
       <c r="H87" s="54"/>
-      <c r="I87" s="145"/>
+      <c r="I87" s="121"/>
       <c r="J87" s="54"/>
       <c r="K87" s="54"/>
       <c r="L87" s="54"/>
@@ -19763,7 +21315,7 @@
       <c r="F88" s="54"/>
       <c r="G88" s="54"/>
       <c r="H88" s="54"/>
-      <c r="I88" s="145"/>
+      <c r="I88" s="121"/>
       <c r="J88" s="54"/>
       <c r="K88" s="54"/>
       <c r="L88" s="54"/>
@@ -19779,7 +21331,7 @@
       <c r="F89" s="54"/>
       <c r="G89" s="54"/>
       <c r="H89" s="54"/>
-      <c r="I89" s="145"/>
+      <c r="I89" s="121"/>
       <c r="J89" s="54"/>
       <c r="K89" s="54"/>
       <c r="L89" s="54"/>
@@ -19795,7 +21347,7 @@
       <c r="F90" s="54"/>
       <c r="G90" s="54"/>
       <c r="H90" s="54"/>
-      <c r="I90" s="145"/>
+      <c r="I90" s="121"/>
       <c r="J90" s="54"/>
       <c r="K90" s="54"/>
       <c r="L90" s="54"/>
@@ -19811,7 +21363,7 @@
       <c r="F91" s="54"/>
       <c r="G91" s="54"/>
       <c r="H91" s="54"/>
-      <c r="I91" s="145"/>
+      <c r="I91" s="121"/>
       <c r="J91" s="54"/>
       <c r="K91" s="54"/>
       <c r="L91" s="54"/>
@@ -19827,7 +21379,7 @@
       <c r="F92" s="54"/>
       <c r="G92" s="54"/>
       <c r="H92" s="54"/>
-      <c r="I92" s="145"/>
+      <c r="I92" s="121"/>
       <c r="J92" s="54"/>
       <c r="K92" s="54"/>
       <c r="L92" s="54"/>
@@ -19843,7 +21395,7 @@
       <c r="F93" s="54"/>
       <c r="G93" s="54"/>
       <c r="H93" s="54"/>
-      <c r="I93" s="145"/>
+      <c r="I93" s="121"/>
       <c r="J93" s="54"/>
       <c r="K93" s="54"/>
       <c r="L93" s="54"/>
@@ -19859,7 +21411,7 @@
       <c r="F94" s="54"/>
       <c r="G94" s="54"/>
       <c r="H94" s="54"/>
-      <c r="I94" s="145"/>
+      <c r="I94" s="121"/>
       <c r="J94" s="54"/>
       <c r="K94" s="54"/>
       <c r="L94" s="54"/>
@@ -19875,7 +21427,7 @@
       <c r="F95" s="54"/>
       <c r="G95" s="54"/>
       <c r="H95" s="54"/>
-      <c r="I95" s="145"/>
+      <c r="I95" s="121"/>
       <c r="J95" s="54"/>
       <c r="K95" s="54"/>
       <c r="L95" s="54"/>
@@ -19891,7 +21443,7 @@
       <c r="F96" s="54"/>
       <c r="G96" s="54"/>
       <c r="H96" s="54"/>
-      <c r="I96" s="145"/>
+      <c r="I96" s="121"/>
       <c r="J96" s="54"/>
       <c r="K96" s="54"/>
       <c r="L96" s="54"/>
@@ -19907,7 +21459,7 @@
       <c r="F97" s="54"/>
       <c r="G97" s="54"/>
       <c r="H97" s="54"/>
-      <c r="I97" s="145"/>
+      <c r="I97" s="121"/>
       <c r="J97" s="54"/>
       <c r="K97" s="54"/>
       <c r="L97" s="54"/>
@@ -19923,7 +21475,7 @@
       <c r="F98" s="54"/>
       <c r="G98" s="54"/>
       <c r="H98" s="54"/>
-      <c r="I98" s="145"/>
+      <c r="I98" s="121"/>
       <c r="J98" s="54"/>
       <c r="K98" s="54"/>
       <c r="L98" s="54"/>
@@ -19939,7 +21491,7 @@
       <c r="F99" s="54"/>
       <c r="G99" s="54"/>
       <c r="H99" s="54"/>
-      <c r="I99" s="145"/>
+      <c r="I99" s="121"/>
       <c r="J99" s="54"/>
       <c r="K99" s="54"/>
       <c r="L99" s="54"/>
@@ -19955,7 +21507,7 @@
       <c r="F100" s="54"/>
       <c r="G100" s="54"/>
       <c r="H100" s="54"/>
-      <c r="I100" s="145"/>
+      <c r="I100" s="121"/>
       <c r="J100" s="54"/>
       <c r="K100" s="54"/>
       <c r="L100" s="54"/>
@@ -19971,7 +21523,7 @@
       <c r="F101" s="54"/>
       <c r="G101" s="54"/>
       <c r="H101" s="54"/>
-      <c r="I101" s="145"/>
+      <c r="I101" s="121"/>
       <c r="J101" s="54"/>
       <c r="K101" s="54"/>
       <c r="L101" s="54"/>
@@ -19987,7 +21539,7 @@
       <c r="F102" s="54"/>
       <c r="G102" s="54"/>
       <c r="H102" s="54"/>
-      <c r="I102" s="145"/>
+      <c r="I102" s="121"/>
       <c r="J102" s="54"/>
       <c r="K102" s="54"/>
       <c r="L102" s="54"/>
@@ -20003,7 +21555,7 @@
       <c r="F103" s="54"/>
       <c r="G103" s="54"/>
       <c r="H103" s="54"/>
-      <c r="I103" s="145"/>
+      <c r="I103" s="121"/>
       <c r="J103" s="54"/>
       <c r="K103" s="54"/>
       <c r="L103" s="54"/>
@@ -20019,7 +21571,7 @@
       <c r="F104" s="54"/>
       <c r="G104" s="54"/>
       <c r="H104" s="54"/>
-      <c r="I104" s="145"/>
+      <c r="I104" s="121"/>
       <c r="J104" s="54"/>
       <c r="K104" s="54"/>
       <c r="L104" s="54"/>
@@ -20035,7 +21587,7 @@
       <c r="F105" s="54"/>
       <c r="G105" s="54"/>
       <c r="H105" s="54"/>
-      <c r="I105" s="145"/>
+      <c r="I105" s="121"/>
       <c r="J105" s="54"/>
       <c r="K105" s="54"/>
       <c r="L105" s="54"/>
@@ -20051,7 +21603,7 @@
       <c r="F106" s="54"/>
       <c r="G106" s="54"/>
       <c r="H106" s="54"/>
-      <c r="I106" s="145"/>
+      <c r="I106" s="121"/>
       <c r="J106" s="54"/>
       <c r="K106" s="54"/>
       <c r="L106" s="54"/>
@@ -20067,7 +21619,7 @@
       <c r="F107" s="54"/>
       <c r="G107" s="54"/>
       <c r="H107" s="54"/>
-      <c r="I107" s="145"/>
+      <c r="I107" s="121"/>
       <c r="J107" s="54"/>
       <c r="K107" s="54"/>
       <c r="L107" s="54"/>
@@ -20083,7 +21635,7 @@
       <c r="F108" s="54"/>
       <c r="G108" s="54"/>
       <c r="H108" s="54"/>
-      <c r="I108" s="145"/>
+      <c r="I108" s="121"/>
       <c r="J108" s="54"/>
       <c r="K108" s="54"/>
       <c r="L108" s="54"/>
@@ -20099,7 +21651,7 @@
       <c r="F109" s="54"/>
       <c r="G109" s="54"/>
       <c r="H109" s="54"/>
-      <c r="I109" s="145"/>
+      <c r="I109" s="121"/>
       <c r="J109" s="54"/>
       <c r="K109" s="54"/>
       <c r="L109" s="54"/>
@@ -20115,7 +21667,7 @@
       <c r="F110" s="54"/>
       <c r="G110" s="54"/>
       <c r="H110" s="54"/>
-      <c r="I110" s="145"/>
+      <c r="I110" s="121"/>
       <c r="J110" s="54"/>
       <c r="K110" s="54"/>
       <c r="L110" s="54"/>
@@ -20131,7 +21683,7 @@
       <c r="F111" s="54"/>
       <c r="G111" s="54"/>
       <c r="H111" s="54"/>
-      <c r="I111" s="145"/>
+      <c r="I111" s="121"/>
       <c r="J111" s="54"/>
       <c r="K111" s="54"/>
       <c r="L111" s="54"/>
@@ -20147,7 +21699,7 @@
       <c r="F112" s="54"/>
       <c r="G112" s="54"/>
       <c r="H112" s="54"/>
-      <c r="I112" s="145"/>
+      <c r="I112" s="121"/>
       <c r="J112" s="54"/>
       <c r="K112" s="54"/>
       <c r="L112" s="54"/>
@@ -20163,7 +21715,7 @@
       <c r="F113" s="54"/>
       <c r="G113" s="54"/>
       <c r="H113" s="54"/>
-      <c r="I113" s="145"/>
+      <c r="I113" s="121"/>
       <c r="J113" s="54"/>
       <c r="K113" s="54"/>
       <c r="L113" s="54"/>
@@ -20179,7 +21731,7 @@
       <c r="F114" s="54"/>
       <c r="G114" s="54"/>
       <c r="H114" s="54"/>
-      <c r="I114" s="145"/>
+      <c r="I114" s="121"/>
       <c r="J114" s="54"/>
       <c r="K114" s="54"/>
       <c r="L114" s="54"/>
@@ -20195,7 +21747,7 @@
       <c r="F115" s="54"/>
       <c r="G115" s="54"/>
       <c r="H115" s="54"/>
-      <c r="I115" s="145"/>
+      <c r="I115" s="121"/>
       <c r="J115" s="54"/>
       <c r="K115" s="54"/>
       <c r="L115" s="54"/>
@@ -20211,7 +21763,7 @@
       <c r="F116" s="54"/>
       <c r="G116" s="54"/>
       <c r="H116" s="54"/>
-      <c r="I116" s="145"/>
+      <c r="I116" s="121"/>
       <c r="J116" s="54"/>
       <c r="K116" s="54"/>
       <c r="L116" s="54"/>
@@ -20227,7 +21779,7 @@
       <c r="F117" s="54"/>
       <c r="G117" s="54"/>
       <c r="H117" s="54"/>
-      <c r="I117" s="145"/>
+      <c r="I117" s="121"/>
       <c r="J117" s="54"/>
       <c r="K117" s="54"/>
       <c r="L117" s="54"/>
@@ -20243,7 +21795,7 @@
       <c r="F118" s="54"/>
       <c r="G118" s="54"/>
       <c r="H118" s="54"/>
-      <c r="I118" s="145"/>
+      <c r="I118" s="121"/>
       <c r="J118" s="54"/>
       <c r="K118" s="54"/>
       <c r="L118" s="54"/>
@@ -20259,7 +21811,7 @@
       <c r="F119" s="54"/>
       <c r="G119" s="54"/>
       <c r="H119" s="54"/>
-      <c r="I119" s="145"/>
+      <c r="I119" s="121"/>
       <c r="J119" s="54"/>
       <c r="K119" s="54"/>
       <c r="L119" s="54"/>
@@ -20275,7 +21827,7 @@
       <c r="F120" s="54"/>
       <c r="G120" s="54"/>
       <c r="H120" s="54"/>
-      <c r="I120" s="145"/>
+      <c r="I120" s="121"/>
       <c r="J120" s="54"/>
       <c r="K120" s="54"/>
       <c r="L120" s="54"/>
@@ -20291,7 +21843,7 @@
       <c r="F121" s="54"/>
       <c r="G121" s="54"/>
       <c r="H121" s="54"/>
-      <c r="I121" s="145"/>
+      <c r="I121" s="121"/>
       <c r="J121" s="54"/>
       <c r="K121" s="54"/>
       <c r="L121" s="54"/>
@@ -20307,7 +21859,7 @@
       <c r="F122" s="54"/>
       <c r="G122" s="54"/>
       <c r="H122" s="54"/>
-      <c r="I122" s="145"/>
+      <c r="I122" s="121"/>
       <c r="J122" s="54"/>
       <c r="K122" s="54"/>
       <c r="L122" s="54"/>
@@ -20323,7 +21875,7 @@
       <c r="F123" s="54"/>
       <c r="G123" s="54"/>
       <c r="H123" s="54"/>
-      <c r="I123" s="145"/>
+      <c r="I123" s="121"/>
       <c r="J123" s="54"/>
       <c r="K123" s="54"/>
       <c r="L123" s="54"/>
@@ -20339,7 +21891,7 @@
       <c r="F124" s="54"/>
       <c r="G124" s="54"/>
       <c r="H124" s="54"/>
-      <c r="I124" s="145"/>
+      <c r="I124" s="121"/>
       <c r="J124" s="54"/>
       <c r="K124" s="54"/>
       <c r="L124" s="54"/>
@@ -20355,7 +21907,7 @@
       <c r="F125" s="54"/>
       <c r="G125" s="54"/>
       <c r="H125" s="54"/>
-      <c r="I125" s="145"/>
+      <c r="I125" s="121"/>
       <c r="J125" s="54"/>
       <c r="K125" s="54"/>
       <c r="L125" s="54"/>
@@ -20371,7 +21923,7 @@
       <c r="F126" s="54"/>
       <c r="G126" s="54"/>
       <c r="H126" s="54"/>
-      <c r="I126" s="145"/>
+      <c r="I126" s="121"/>
       <c r="J126" s="54"/>
       <c r="K126" s="54"/>
       <c r="L126" s="54"/>
@@ -20387,7 +21939,7 @@
       <c r="F127" s="54"/>
       <c r="G127" s="54"/>
       <c r="H127" s="54"/>
-      <c r="I127" s="145"/>
+      <c r="I127" s="121"/>
       <c r="J127" s="54"/>
       <c r="K127" s="54"/>
       <c r="L127" s="54"/>
@@ -20403,7 +21955,7 @@
       <c r="F128" s="54"/>
       <c r="G128" s="54"/>
       <c r="H128" s="54"/>
-      <c r="I128" s="145"/>
+      <c r="I128" s="121"/>
       <c r="J128" s="54"/>
       <c r="K128" s="54"/>
       <c r="L128" s="54"/>
@@ -20419,7 +21971,7 @@
       <c r="F129" s="54"/>
       <c r="G129" s="54"/>
       <c r="H129" s="54"/>
-      <c r="I129" s="145"/>
+      <c r="I129" s="121"/>
       <c r="J129" s="54"/>
       <c r="K129" s="54"/>
       <c r="L129" s="54"/>
@@ -20435,7 +21987,7 @@
       <c r="F130" s="54"/>
       <c r="G130" s="54"/>
       <c r="H130" s="54"/>
-      <c r="I130" s="145"/>
+      <c r="I130" s="121"/>
       <c r="J130" s="54"/>
       <c r="K130" s="54"/>
       <c r="L130" s="54"/>
@@ -20451,7 +22003,7 @@
       <c r="F131" s="54"/>
       <c r="G131" s="54"/>
       <c r="H131" s="54"/>
-      <c r="I131" s="145"/>
+      <c r="I131" s="121"/>
       <c r="J131" s="54"/>
       <c r="K131" s="54"/>
       <c r="L131" s="54"/>
@@ -20467,7 +22019,7 @@
       <c r="F132" s="54"/>
       <c r="G132" s="54"/>
       <c r="H132" s="54"/>
-      <c r="I132" s="145"/>
+      <c r="I132" s="121"/>
       <c r="J132" s="54"/>
       <c r="K132" s="54"/>
       <c r="L132" s="54"/>
@@ -20483,7 +22035,7 @@
       <c r="F133" s="54"/>
       <c r="G133" s="54"/>
       <c r="H133" s="54"/>
-      <c r="I133" s="145"/>
+      <c r="I133" s="121"/>
       <c r="J133" s="54"/>
       <c r="K133" s="54"/>
       <c r="L133" s="54"/>
@@ -20499,7 +22051,7 @@
       <c r="F134" s="54"/>
       <c r="G134" s="54"/>
       <c r="H134" s="54"/>
-      <c r="I134" s="145"/>
+      <c r="I134" s="121"/>
       <c r="J134" s="54"/>
       <c r="K134" s="54"/>
       <c r="L134" s="54"/>
@@ -20515,7 +22067,7 @@
       <c r="F135" s="54"/>
       <c r="G135" s="54"/>
       <c r="H135" s="54"/>
-      <c r="I135" s="145"/>
+      <c r="I135" s="121"/>
       <c r="J135" s="54"/>
       <c r="K135" s="54"/>
       <c r="L135" s="54"/>
@@ -20531,7 +22083,7 @@
       <c r="F136" s="54"/>
       <c r="G136" s="54"/>
       <c r="H136" s="54"/>
-      <c r="I136" s="145"/>
+      <c r="I136" s="121"/>
       <c r="J136" s="54"/>
       <c r="K136" s="54"/>
       <c r="L136" s="54"/>
@@ -20547,7 +22099,7 @@
       <c r="F137" s="54"/>
       <c r="G137" s="54"/>
       <c r="H137" s="54"/>
-      <c r="I137" s="145"/>
+      <c r="I137" s="121"/>
       <c r="J137" s="54"/>
       <c r="K137" s="54"/>
       <c r="L137" s="54"/>
@@ -20563,7 +22115,7 @@
       <c r="F138" s="54"/>
       <c r="G138" s="54"/>
       <c r="H138" s="54"/>
-      <c r="I138" s="145"/>
+      <c r="I138" s="121"/>
       <c r="J138" s="54"/>
       <c r="K138" s="54"/>
       <c r="L138" s="54"/>
@@ -20579,7 +22131,7 @@
       <c r="F139" s="54"/>
       <c r="G139" s="54"/>
       <c r="H139" s="54"/>
-      <c r="I139" s="145"/>
+      <c r="I139" s="121"/>
       <c r="J139" s="54"/>
       <c r="K139" s="54"/>
       <c r="L139" s="54"/>
@@ -20595,7 +22147,7 @@
       <c r="F140" s="54"/>
       <c r="G140" s="54"/>
       <c r="H140" s="54"/>
-      <c r="I140" s="145"/>
+      <c r="I140" s="121"/>
       <c r="J140" s="54"/>
       <c r="K140" s="54"/>
       <c r="L140" s="54"/>
@@ -20611,7 +22163,7 @@
       <c r="F141" s="54"/>
       <c r="G141" s="54"/>
       <c r="H141" s="54"/>
-      <c r="I141" s="145"/>
+      <c r="I141" s="121"/>
       <c r="J141" s="54"/>
       <c r="K141" s="54"/>
       <c r="L141" s="54"/>
@@ -20627,7 +22179,7 @@
       <c r="F142" s="54"/>
       <c r="G142" s="54"/>
       <c r="H142" s="54"/>
-      <c r="I142" s="145"/>
+      <c r="I142" s="121"/>
       <c r="J142" s="54"/>
       <c r="K142" s="54"/>
       <c r="L142" s="54"/>
@@ -20643,7 +22195,7 @@
       <c r="F143" s="54"/>
       <c r="G143" s="54"/>
       <c r="H143" s="54"/>
-      <c r="I143" s="145"/>
+      <c r="I143" s="121"/>
       <c r="J143" s="54"/>
       <c r="K143" s="54"/>
       <c r="L143" s="54"/>
@@ -20659,7 +22211,7 @@
       <c r="F144" s="54"/>
       <c r="G144" s="54"/>
       <c r="H144" s="54"/>
-      <c r="I144" s="145"/>
+      <c r="I144" s="121"/>
       <c r="J144" s="54"/>
       <c r="K144" s="54"/>
       <c r="L144" s="54"/>
@@ -20675,7 +22227,7 @@
       <c r="F145" s="54"/>
       <c r="G145" s="54"/>
       <c r="H145" s="54"/>
-      <c r="I145" s="145"/>
+      <c r="I145" s="121"/>
       <c r="J145" s="54"/>
       <c r="K145" s="54"/>
       <c r="L145" s="54"/>
@@ -20691,7 +22243,7 @@
       <c r="F146" s="54"/>
       <c r="G146" s="54"/>
       <c r="H146" s="54"/>
-      <c r="I146" s="145"/>
+      <c r="I146" s="121"/>
       <c r="J146" s="54"/>
       <c r="K146" s="54"/>
       <c r="L146" s="54"/>
@@ -20707,7 +22259,7 @@
       <c r="F147" s="54"/>
       <c r="G147" s="54"/>
       <c r="H147" s="54"/>
-      <c r="I147" s="145"/>
+      <c r="I147" s="121"/>
       <c r="J147" s="54"/>
       <c r="K147" s="54"/>
       <c r="L147" s="54"/>
@@ -20723,7 +22275,7 @@
       <c r="F148" s="54"/>
       <c r="G148" s="54"/>
       <c r="H148" s="54"/>
-      <c r="I148" s="145"/>
+      <c r="I148" s="121"/>
       <c r="J148" s="54"/>
       <c r="K148" s="54"/>
       <c r="L148" s="54"/>
@@ -20739,7 +22291,7 @@
       <c r="F149" s="54"/>
       <c r="G149" s="54"/>
       <c r="H149" s="54"/>
-      <c r="I149" s="145"/>
+      <c r="I149" s="121"/>
       <c r="J149" s="54"/>
       <c r="K149" s="54"/>
       <c r="L149" s="54"/>
@@ -20755,7 +22307,7 @@
       <c r="F150" s="54"/>
       <c r="G150" s="54"/>
       <c r="H150" s="54"/>
-      <c r="I150" s="145"/>
+      <c r="I150" s="121"/>
       <c r="J150" s="54"/>
       <c r="K150" s="54"/>
       <c r="L150" s="54"/>
@@ -20771,7 +22323,7 @@
       <c r="F151" s="54"/>
       <c r="G151" s="54"/>
       <c r="H151" s="54"/>
-      <c r="I151" s="145"/>
+      <c r="I151" s="121"/>
       <c r="J151" s="54"/>
       <c r="K151" s="54"/>
       <c r="L151" s="54"/>
@@ -20787,7 +22339,7 @@
       <c r="F152" s="54"/>
       <c r="G152" s="54"/>
       <c r="H152" s="54"/>
-      <c r="I152" s="145"/>
+      <c r="I152" s="121"/>
       <c r="J152" s="54"/>
       <c r="K152" s="54"/>
       <c r="L152" s="54"/>
@@ -20803,7 +22355,7 @@
       <c r="F153" s="54"/>
       <c r="G153" s="54"/>
       <c r="H153" s="54"/>
-      <c r="I153" s="145"/>
+      <c r="I153" s="121"/>
       <c r="J153" s="54"/>
       <c r="K153" s="54"/>
       <c r="L153" s="54"/>
@@ -20819,7 +22371,7 @@
       <c r="F154" s="54"/>
       <c r="G154" s="54"/>
       <c r="H154" s="54"/>
-      <c r="I154" s="145"/>
+      <c r="I154" s="121"/>
       <c r="J154" s="54"/>
       <c r="K154" s="54"/>
       <c r="L154" s="54"/>
@@ -20835,7 +22387,7 @@
       <c r="F155" s="54"/>
       <c r="G155" s="54"/>
       <c r="H155" s="54"/>
-      <c r="I155" s="145"/>
+      <c r="I155" s="121"/>
       <c r="J155" s="54"/>
       <c r="K155" s="54"/>
       <c r="L155" s="54"/>
@@ -20851,7 +22403,7 @@
       <c r="F156" s="54"/>
       <c r="G156" s="54"/>
       <c r="H156" s="54"/>
-      <c r="I156" s="145"/>
+      <c r="I156" s="121"/>
       <c r="J156" s="54"/>
       <c r="K156" s="54"/>
       <c r="L156" s="54"/>
@@ -20867,7 +22419,7 @@
       <c r="F157" s="54"/>
       <c r="G157" s="54"/>
       <c r="H157" s="54"/>
-      <c r="I157" s="145"/>
+      <c r="I157" s="121"/>
       <c r="J157" s="54"/>
       <c r="K157" s="54"/>
       <c r="L157" s="54"/>
@@ -20883,7 +22435,7 @@
       <c r="F158" s="54"/>
       <c r="G158" s="54"/>
       <c r="H158" s="54"/>
-      <c r="I158" s="145"/>
+      <c r="I158" s="121"/>
       <c r="J158" s="54"/>
       <c r="K158" s="54"/>
       <c r="L158" s="54"/>
@@ -20899,7 +22451,7 @@
       <c r="F159" s="54"/>
       <c r="G159" s="54"/>
       <c r="H159" s="54"/>
-      <c r="I159" s="145"/>
+      <c r="I159" s="121"/>
       <c r="J159" s="54"/>
       <c r="K159" s="54"/>
       <c r="L159" s="54"/>
@@ -20915,7 +22467,7 @@
       <c r="F160" s="54"/>
       <c r="G160" s="54"/>
       <c r="H160" s="54"/>
-      <c r="I160" s="145"/>
+      <c r="I160" s="121"/>
       <c r="J160" s="54"/>
       <c r="K160" s="54"/>
       <c r="L160" s="54"/>
@@ -20931,7 +22483,7 @@
       <c r="F161" s="54"/>
       <c r="G161" s="54"/>
       <c r="H161" s="54"/>
-      <c r="I161" s="145"/>
+      <c r="I161" s="121"/>
       <c r="J161" s="54"/>
       <c r="K161" s="54"/>
       <c r="L161" s="54"/>
@@ -20947,7 +22499,7 @@
       <c r="F162" s="54"/>
       <c r="G162" s="54"/>
       <c r="H162" s="54"/>
-      <c r="I162" s="145"/>
+      <c r="I162" s="121"/>
       <c r="J162" s="54"/>
       <c r="K162" s="54"/>
       <c r="L162" s="54"/>
@@ -20963,7 +22515,7 @@
       <c r="F163" s="54"/>
       <c r="G163" s="54"/>
       <c r="H163" s="54"/>
-      <c r="I163" s="145"/>
+      <c r="I163" s="121"/>
       <c r="J163" s="54"/>
       <c r="K163" s="54"/>
       <c r="L163" s="54"/>
@@ -20979,7 +22531,7 @@
       <c r="F164" s="54"/>
       <c r="G164" s="54"/>
       <c r="H164" s="54"/>
-      <c r="I164" s="145"/>
+      <c r="I164" s="121"/>
       <c r="J164" s="54"/>
       <c r="K164" s="54"/>
       <c r="L164" s="54"/>
@@ -20995,7 +22547,7 @@
       <c r="F165" s="54"/>
       <c r="G165" s="54"/>
       <c r="H165" s="54"/>
-      <c r="I165" s="145"/>
+      <c r="I165" s="121"/>
       <c r="J165" s="54"/>
       <c r="K165" s="54"/>
       <c r="L165" s="54"/>
@@ -21011,7 +22563,7 @@
       <c r="F166" s="54"/>
       <c r="G166" s="54"/>
       <c r="H166" s="54"/>
-      <c r="I166" s="145"/>
+      <c r="I166" s="121"/>
       <c r="J166" s="54"/>
       <c r="K166" s="54"/>
       <c r="L166" s="54"/>
@@ -21027,7 +22579,7 @@
       <c r="F167" s="54"/>
       <c r="G167" s="54"/>
       <c r="H167" s="54"/>
-      <c r="I167" s="145"/>
+      <c r="I167" s="121"/>
       <c r="J167" s="54"/>
       <c r="K167" s="54"/>
       <c r="L167" s="54"/>
@@ -21043,7 +22595,7 @@
       <c r="F168" s="54"/>
       <c r="G168" s="54"/>
       <c r="H168" s="54"/>
-      <c r="I168" s="145"/>
+      <c r="I168" s="121"/>
       <c r="J168" s="54"/>
       <c r="K168" s="54"/>
       <c r="L168" s="54"/>
@@ -21059,7 +22611,7 @@
       <c r="F169" s="54"/>
       <c r="G169" s="54"/>
       <c r="H169" s="54"/>
-      <c r="I169" s="145"/>
+      <c r="I169" s="121"/>
       <c r="J169" s="54"/>
       <c r="K169" s="54"/>
       <c r="L169" s="54"/>
@@ -21075,7 +22627,7 @@
       <c r="F170" s="54"/>
       <c r="G170" s="54"/>
       <c r="H170" s="54"/>
-      <c r="I170" s="145"/>
+      <c r="I170" s="121"/>
       <c r="J170" s="54"/>
       <c r="K170" s="54"/>
       <c r="L170" s="54"/>
@@ -21091,7 +22643,7 @@
       <c r="F171" s="54"/>
       <c r="G171" s="54"/>
       <c r="H171" s="54"/>
-      <c r="I171" s="145"/>
+      <c r="I171" s="121"/>
       <c r="J171" s="54"/>
       <c r="K171" s="54"/>
       <c r="L171" s="54"/>
@@ -21107,7 +22659,7 @@
       <c r="F172" s="54"/>
       <c r="G172" s="54"/>
       <c r="H172" s="54"/>
-      <c r="I172" s="145"/>
+      <c r="I172" s="121"/>
       <c r="J172" s="54"/>
       <c r="K172" s="54"/>
       <c r="L172" s="54"/>
@@ -21123,7 +22675,7 @@
       <c r="F173" s="54"/>
       <c r="G173" s="54"/>
       <c r="H173" s="54"/>
-      <c r="I173" s="145"/>
+      <c r="I173" s="121"/>
       <c r="J173" s="54"/>
       <c r="K173" s="54"/>
       <c r="L173" s="54"/>
@@ -21139,7 +22691,7 @@
       <c r="F174" s="54"/>
       <c r="G174" s="54"/>
       <c r="H174" s="54"/>
-      <c r="I174" s="145"/>
+      <c r="I174" s="121"/>
       <c r="J174" s="54"/>
       <c r="K174" s="54"/>
       <c r="L174" s="54"/>
@@ -21155,7 +22707,7 @@
       <c r="F175" s="54"/>
       <c r="G175" s="54"/>
       <c r="H175" s="54"/>
-      <c r="I175" s="145"/>
+      <c r="I175" s="121"/>
       <c r="J175" s="54"/>
       <c r="K175" s="54"/>
       <c r="L175" s="54"/>
@@ -21171,7 +22723,7 @@
       <c r="F176" s="54"/>
       <c r="G176" s="54"/>
       <c r="H176" s="54"/>
-      <c r="I176" s="145"/>
+      <c r="I176" s="121"/>
       <c r="J176" s="54"/>
       <c r="K176" s="54"/>
       <c r="L176" s="54"/>
@@ -21187,7 +22739,7 @@
       <c r="F177" s="54"/>
       <c r="G177" s="54"/>
       <c r="H177" s="54"/>
-      <c r="I177" s="145"/>
+      <c r="I177" s="121"/>
       <c r="J177" s="54"/>
       <c r="K177" s="54"/>
       <c r="L177" s="54"/>
@@ -21203,7 +22755,7 @@
       <c r="F178" s="54"/>
       <c r="G178" s="54"/>
       <c r="H178" s="54"/>
-      <c r="I178" s="145"/>
+      <c r="I178" s="121"/>
       <c r="J178" s="54"/>
       <c r="K178" s="54"/>
       <c r="L178" s="54"/>
@@ -21219,7 +22771,7 @@
       <c r="F179" s="54"/>
       <c r="G179" s="54"/>
       <c r="H179" s="54"/>
-      <c r="I179" s="145"/>
+      <c r="I179" s="121"/>
       <c r="J179" s="54"/>
       <c r="K179" s="54"/>
       <c r="L179" s="54"/>
@@ -21235,7 +22787,7 @@
       <c r="F180" s="54"/>
       <c r="G180" s="54"/>
       <c r="H180" s="54"/>
-      <c r="I180" s="145"/>
+      <c r="I180" s="121"/>
       <c r="J180" s="54"/>
       <c r="K180" s="54"/>
       <c r="L180" s="54"/>
@@ -21251,7 +22803,7 @@
       <c r="F181" s="54"/>
       <c r="G181" s="54"/>
       <c r="H181" s="54"/>
-      <c r="I181" s="145"/>
+      <c r="I181" s="121"/>
       <c r="J181" s="54"/>
       <c r="K181" s="54"/>
       <c r="L181" s="54"/>
@@ -21267,7 +22819,7 @@
       <c r="F182" s="54"/>
       <c r="G182" s="54"/>
       <c r="H182" s="54"/>
-      <c r="I182" s="145"/>
+      <c r="I182" s="121"/>
       <c r="J182" s="54"/>
       <c r="K182" s="54"/>
       <c r="L182" s="54"/>
@@ -21283,7 +22835,7 @@
       <c r="F183" s="54"/>
       <c r="G183" s="54"/>
       <c r="H183" s="54"/>
-      <c r="I183" s="145"/>
+      <c r="I183" s="121"/>
       <c r="J183" s="54"/>
       <c r="K183" s="54"/>
       <c r="L183" s="54"/>
@@ -21299,7 +22851,7 @@
       <c r="F184" s="54"/>
       <c r="G184" s="54"/>
       <c r="H184" s="54"/>
-      <c r="I184" s="145"/>
+      <c r="I184" s="121"/>
       <c r="J184" s="54"/>
       <c r="K184" s="54"/>
       <c r="L184" s="54"/>
@@ -21315,7 +22867,7 @@
       <c r="F185" s="54"/>
       <c r="G185" s="54"/>
       <c r="H185" s="54"/>
-      <c r="I185" s="145"/>
+      <c r="I185" s="121"/>
       <c r="J185" s="54"/>
       <c r="K185" s="54"/>
       <c r="L185" s="54"/>
@@ -21331,7 +22883,7 @@
       <c r="F186" s="54"/>
       <c r="G186" s="54"/>
       <c r="H186" s="54"/>
-      <c r="I186" s="145"/>
+      <c r="I186" s="121"/>
       <c r="J186" s="54"/>
       <c r="K186" s="54"/>
       <c r="L186" s="54"/>
@@ -21347,7 +22899,7 @@
       <c r="F187" s="54"/>
       <c r="G187" s="54"/>
       <c r="H187" s="54"/>
-      <c r="I187" s="145"/>
+      <c r="I187" s="121"/>
       <c r="J187" s="54"/>
       <c r="K187" s="54"/>
       <c r="L187" s="54"/>
@@ -21363,7 +22915,7 @@
       <c r="F188" s="54"/>
       <c r="G188" s="54"/>
       <c r="H188" s="54"/>
-      <c r="I188" s="145"/>
+      <c r="I188" s="121"/>
       <c r="J188" s="54"/>
       <c r="K188" s="54"/>
       <c r="L188" s="54"/>
@@ -21379,7 +22931,7 @@
       <c r="F189" s="54"/>
       <c r="G189" s="54"/>
       <c r="H189" s="54"/>
-      <c r="I189" s="145"/>
+      <c r="I189" s="121"/>
       <c r="J189" s="54"/>
       <c r="K189" s="54"/>
       <c r="L189" s="54"/>
@@ -21395,7 +22947,7 @@
       <c r="F190" s="54"/>
       <c r="G190" s="54"/>
       <c r="H190" s="54"/>
-      <c r="I190" s="145"/>
+      <c r="I190" s="121"/>
       <c r="J190" s="54"/>
       <c r="K190" s="54"/>
       <c r="L190" s="54"/>
@@ -21411,7 +22963,7 @@
       <c r="F191" s="54"/>
       <c r="G191" s="54"/>
       <c r="H191" s="54"/>
-      <c r="I191" s="145"/>
+      <c r="I191" s="121"/>
       <c r="J191" s="54"/>
       <c r="K191" s="54"/>
       <c r="L191" s="54"/>
@@ -21427,7 +22979,7 @@
       <c r="F192" s="54"/>
       <c r="G192" s="54"/>
       <c r="H192" s="54"/>
-      <c r="I192" s="145"/>
+      <c r="I192" s="121"/>
       <c r="J192" s="54"/>
       <c r="K192" s="54"/>
       <c r="L192" s="54"/>
@@ -21443,7 +22995,7 @@
       <c r="F193" s="54"/>
       <c r="G193" s="54"/>
       <c r="H193" s="54"/>
-      <c r="I193" s="145"/>
+      <c r="I193" s="121"/>
       <c r="J193" s="54"/>
       <c r="K193" s="54"/>
       <c r="L193" s="54"/>
@@ -21459,7 +23011,7 @@
       <c r="F194" s="54"/>
       <c r="G194" s="54"/>
       <c r="H194" s="54"/>
-      <c r="I194" s="145"/>
+      <c r="I194" s="121"/>
       <c r="J194" s="54"/>
       <c r="K194" s="54"/>
       <c r="L194" s="54"/>
@@ -21475,7 +23027,7 @@
       <c r="F195" s="54"/>
       <c r="G195" s="54"/>
       <c r="H195" s="54"/>
-      <c r="I195" s="145"/>
+      <c r="I195" s="121"/>
       <c r="J195" s="54"/>
       <c r="K195" s="54"/>
       <c r="L195" s="54"/>
@@ -21491,7 +23043,7 @@
       <c r="F196" s="54"/>
       <c r="G196" s="54"/>
       <c r="H196" s="54"/>
-      <c r="I196" s="145"/>
+      <c r="I196" s="121"/>
       <c r="J196" s="54"/>
       <c r="K196" s="54"/>
       <c r="L196" s="54"/>
@@ -21507,7 +23059,7 @@
       <c r="F197" s="54"/>
       <c r="G197" s="54"/>
       <c r="H197" s="54"/>
-      <c r="I197" s="145"/>
+      <c r="I197" s="121"/>
       <c r="J197" s="54"/>
       <c r="K197" s="54"/>
       <c r="L197" s="54"/>
@@ -21523,7 +23075,7 @@
       <c r="F198" s="54"/>
       <c r="G198" s="54"/>
       <c r="H198" s="54"/>
-      <c r="I198" s="145"/>
+      <c r="I198" s="121"/>
       <c r="J198" s="54"/>
       <c r="K198" s="54"/>
       <c r="L198" s="54"/>
@@ -21539,7 +23091,7 @@
       <c r="F199" s="54"/>
       <c r="G199" s="54"/>
       <c r="H199" s="54"/>
-      <c r="I199" s="145"/>
+      <c r="I199" s="121"/>
       <c r="J199" s="54"/>
       <c r="K199" s="54"/>
       <c r="L199" s="54"/>
@@ -21555,7 +23107,7 @@
       <c r="F200" s="54"/>
       <c r="G200" s="54"/>
       <c r="H200" s="54"/>
-      <c r="I200" s="145"/>
+      <c r="I200" s="121"/>
       <c r="J200" s="54"/>
       <c r="K200" s="54"/>
       <c r="L200" s="54"/>
@@ -21571,7 +23123,7 @@
       <c r="F201" s="54"/>
       <c r="G201" s="54"/>
       <c r="H201" s="54"/>
-      <c r="I201" s="145"/>
+      <c r="I201" s="121"/>
       <c r="J201" s="54"/>
       <c r="K201" s="54"/>
       <c r="L201" s="54"/>
@@ -21587,7 +23139,7 @@
       <c r="F202" s="54"/>
       <c r="G202" s="54"/>
       <c r="H202" s="54"/>
-      <c r="I202" s="145"/>
+      <c r="I202" s="121"/>
       <c r="J202" s="54"/>
       <c r="K202" s="54"/>
       <c r="L202" s="54"/>
@@ -21603,7 +23155,7 @@
       <c r="F203" s="54"/>
       <c r="G203" s="54"/>
       <c r="H203" s="54"/>
-      <c r="I203" s="145"/>
+      <c r="I203" s="121"/>
       <c r="J203" s="54"/>
       <c r="K203" s="54"/>
       <c r="L203" s="54"/>
@@ -21619,7 +23171,7 @@
       <c r="F204" s="54"/>
       <c r="G204" s="54"/>
       <c r="H204" s="54"/>
-      <c r="I204" s="145"/>
+      <c r="I204" s="121"/>
       <c r="J204" s="54"/>
       <c r="K204" s="54"/>
       <c r="L204" s="54"/>
@@ -21635,7 +23187,7 @@
       <c r="F205" s="54"/>
       <c r="G205" s="54"/>
       <c r="H205" s="54"/>
-      <c r="I205" s="145"/>
+      <c r="I205" s="121"/>
       <c r="J205" s="54"/>
       <c r="K205" s="54"/>
       <c r="L205" s="54"/>
@@ -21651,7 +23203,7 @@
       <c r="F206" s="54"/>
       <c r="G206" s="54"/>
       <c r="H206" s="54"/>
-      <c r="I206" s="145"/>
+      <c r="I206" s="121"/>
       <c r="J206" s="54"/>
       <c r="K206" s="54"/>
       <c r="L206" s="54"/>
@@ -21667,7 +23219,7 @@
       <c r="F207" s="54"/>
       <c r="G207" s="54"/>
       <c r="H207" s="54"/>
-      <c r="I207" s="145"/>
+      <c r="I207" s="121"/>
       <c r="J207" s="54"/>
       <c r="K207" s="54"/>
       <c r="L207" s="54"/>
@@ -21683,7 +23235,7 @@
       <c r="F208" s="54"/>
       <c r="G208" s="54"/>
       <c r="H208" s="54"/>
-      <c r="I208" s="145"/>
+      <c r="I208" s="121"/>
       <c r="J208" s="54"/>
       <c r="K208" s="54"/>
       <c r="L208" s="54"/>
@@ -21699,7 +23251,7 @@
       <c r="F209" s="54"/>
       <c r="G209" s="54"/>
       <c r="H209" s="54"/>
-      <c r="I209" s="145"/>
+      <c r="I209" s="121"/>
       <c r="J209" s="54"/>
       <c r="K209" s="54"/>
       <c r="L209" s="54"/>
@@ -21715,7 +23267,7 @@
       <c r="F210" s="54"/>
       <c r="G210" s="54"/>
       <c r="H210" s="54"/>
-      <c r="I210" s="145"/>
+      <c r="I210" s="121"/>
       <c r="J210" s="54"/>
       <c r="K210" s="54"/>
       <c r="L210" s="54"/>
@@ -21731,7 +23283,7 @@
       <c r="F211" s="54"/>
       <c r="G211" s="54"/>
       <c r="H211" s="54"/>
-      <c r="I211" s="145"/>
+      <c r="I211" s="121"/>
       <c r="J211" s="54"/>
       <c r="K211" s="54"/>
       <c r="L211" s="54"/>
@@ -21747,7 +23299,7 @@
       <c r="F212" s="54"/>
       <c r="G212" s="54"/>
       <c r="H212" s="54"/>
-      <c r="I212" s="145"/>
+      <c r="I212" s="121"/>
       <c r="J212" s="54"/>
       <c r="K212" s="54"/>
       <c r="L212" s="54"/>
@@ -21763,7 +23315,7 @@
       <c r="F213" s="54"/>
       <c r="G213" s="54"/>
       <c r="H213" s="54"/>
-      <c r="I213" s="145"/>
+      <c r="I213" s="121"/>
       <c r="J213" s="54"/>
       <c r="K213" s="54"/>
       <c r="L213" s="54"/>
@@ -21779,7 +23331,7 @@
       <c r="F214" s="54"/>
       <c r="G214" s="54"/>
       <c r="H214" s="54"/>
-      <c r="I214" s="145"/>
+      <c r="I214" s="121"/>
       <c r="J214" s="54"/>
       <c r="K214" s="54"/>
       <c r="L214" s="54"/>
@@ -21795,7 +23347,7 @@
       <c r="F215" s="54"/>
       <c r="G215" s="54"/>
       <c r="H215" s="54"/>
-      <c r="I215" s="145"/>
+      <c r="I215" s="121"/>
       <c r="J215" s="54"/>
       <c r="K215" s="54"/>
       <c r="L215" s="54"/>
@@ -21811,7 +23363,7 @@
       <c r="F216" s="54"/>
       <c r="G216" s="54"/>
       <c r="H216" s="54"/>
-      <c r="I216" s="145"/>
+      <c r="I216" s="121"/>
       <c r="J216" s="54"/>
       <c r="K216" s="54"/>
       <c r="L216" s="54"/>
@@ -21827,7 +23379,7 @@
       <c r="F217" s="54"/>
       <c r="G217" s="54"/>
       <c r="H217" s="54"/>
-      <c r="I217" s="145"/>
+      <c r="I217" s="121"/>
       <c r="J217" s="54"/>
       <c r="K217" s="54"/>
       <c r="L217" s="54"/>
@@ -21843,7 +23395,7 @@
       <c r="F218" s="54"/>
       <c r="G218" s="54"/>
       <c r="H218" s="54"/>
-      <c r="I218" s="145"/>
+      <c r="I218" s="121"/>
       <c r="J218" s="54"/>
       <c r="K218" s="54"/>
       <c r="L218" s="54"/>
@@ -21859,7 +23411,7 @@
       <c r="F219" s="54"/>
       <c r="G219" s="54"/>
       <c r="H219" s="54"/>
-      <c r="I219" s="145"/>
+      <c r="I219" s="121"/>
       <c r="J219" s="54"/>
       <c r="K219" s="54"/>
       <c r="L219" s="54"/>
@@ -21875,7 +23427,7 @@
       <c r="F220" s="54"/>
       <c r="G220" s="54"/>
       <c r="H220" s="54"/>
-      <c r="I220" s="145"/>
+      <c r="I220" s="121"/>
       <c r="J220" s="54"/>
       <c r="K220" s="54"/>
       <c r="L220" s="54"/>
@@ -21891,7 +23443,7 @@
       <c r="F221" s="54"/>
       <c r="G221" s="54"/>
       <c r="H221" s="54"/>
-      <c r="I221" s="145"/>
+      <c r="I221" s="121"/>
       <c r="J221" s="54"/>
       <c r="K221" s="54"/>
       <c r="L221" s="54"/>
@@ -21907,7 +23459,7 @@
       <c r="F222" s="54"/>
       <c r="G222" s="54"/>
       <c r="H222" s="54"/>
-      <c r="I222" s="145"/>
+      <c r="I222" s="121"/>
       <c r="J222" s="54"/>
       <c r="K222" s="54"/>
       <c r="L222" s="54"/>
@@ -21923,7 +23475,7 @@
       <c r="F223" s="54"/>
       <c r="G223" s="54"/>
       <c r="H223" s="54"/>
-      <c r="I223" s="145"/>
+      <c r="I223" s="121"/>
       <c r="J223" s="54"/>
       <c r="K223" s="54"/>
       <c r="L223" s="54"/>
@@ -21939,7 +23491,7 @@
       <c r="F224" s="54"/>
       <c r="G224" s="54"/>
       <c r="H224" s="54"/>
-      <c r="I224" s="145"/>
+      <c r="I224" s="121"/>
       <c r="J224" s="54"/>
       <c r="K224" s="54"/>
       <c r="L224" s="54"/>
@@ -21955,7 +23507,7 @@
       <c r="F225" s="54"/>
       <c r="G225" s="54"/>
       <c r="H225" s="54"/>
-      <c r="I225" s="145"/>
+      <c r="I225" s="121"/>
       <c r="J225" s="54"/>
       <c r="K225" s="54"/>
       <c r="L225" s="54"/>
@@ -21971,7 +23523,7 @@
       <c r="F226" s="54"/>
       <c r="G226" s="54"/>
       <c r="H226" s="54"/>
-      <c r="I226" s="145"/>
+      <c r="I226" s="121"/>
       <c r="J226" s="54"/>
       <c r="K226" s="54"/>
       <c r="L226" s="54"/>
@@ -21987,7 +23539,7 @@
       <c r="F227" s="54"/>
       <c r="G227" s="54"/>
       <c r="H227" s="54"/>
-      <c r="I227" s="145"/>
+      <c r="I227" s="121"/>
       <c r="J227" s="54"/>
       <c r="K227" s="54"/>
       <c r="L227" s="54"/>
@@ -22003,7 +23555,7 @@
       <c r="F228" s="54"/>
       <c r="G228" s="54"/>
       <c r="H228" s="54"/>
-      <c r="I228" s="145"/>
+      <c r="I228" s="121"/>
       <c r="J228" s="54"/>
       <c r="K228" s="54"/>
       <c r="L228" s="54"/>
@@ -22019,7 +23571,7 @@
       <c r="F229" s="54"/>
       <c r="G229" s="54"/>
       <c r="H229" s="54"/>
-      <c r="I229" s="145"/>
+      <c r="I229" s="121"/>
       <c r="J229" s="54"/>
       <c r="K229" s="54"/>
       <c r="L229" s="54"/>
@@ -22035,7 +23587,7 @@
       <c r="F230" s="54"/>
       <c r="G230" s="54"/>
       <c r="H230" s="54"/>
-      <c r="I230" s="145"/>
+      <c r="I230" s="121"/>
       <c r="J230" s="54"/>
       <c r="K230" s="54"/>
       <c r="L230" s="54"/>
@@ -22051,7 +23603,7 @@
       <c r="F231" s="54"/>
       <c r="G231" s="54"/>
       <c r="H231" s="54"/>
-      <c r="I231" s="145"/>
+      <c r="I231" s="121"/>
       <c r="J231" s="54"/>
       <c r="K231" s="54"/>
       <c r="L231" s="54"/>
@@ -22067,7 +23619,7 @@
       <c r="F232" s="54"/>
       <c r="G232" s="54"/>
       <c r="H232" s="54"/>
-      <c r="I232" s="145"/>
+      <c r="I232" s="121"/>
       <c r="J232" s="54"/>
       <c r="K232" s="54"/>
       <c r="L232" s="54"/>
@@ -22083,7 +23635,7 @@
       <c r="F233" s="54"/>
       <c r="G233" s="54"/>
       <c r="H233" s="54"/>
-      <c r="I233" s="145"/>
+      <c r="I233" s="121"/>
       <c r="J233" s="54"/>
       <c r="K233" s="54"/>
       <c r="L233" s="54"/>
@@ -22099,7 +23651,7 @@
       <c r="F234" s="54"/>
       <c r="G234" s="54"/>
       <c r="H234" s="54"/>
-      <c r="I234" s="145"/>
+      <c r="I234" s="121"/>
       <c r="J234" s="54"/>
       <c r="K234" s="54"/>
       <c r="L234" s="54"/>
@@ -22115,7 +23667,7 @@
       <c r="F235" s="54"/>
       <c r="G235" s="54"/>
       <c r="H235" s="54"/>
-      <c r="I235" s="145"/>
+      <c r="I235" s="121"/>
       <c r="J235" s="54"/>
       <c r="K235" s="54"/>
       <c r="L235" s="54"/>
@@ -22131,7 +23683,7 @@
       <c r="F236" s="54"/>
       <c r="G236" s="54"/>
       <c r="H236" s="54"/>
-      <c r="I236" s="145"/>
+      <c r="I236" s="121"/>
       <c r="J236" s="54"/>
       <c r="K236" s="54"/>
       <c r="L236" s="54"/>
@@ -22147,7 +23699,7 @@
       <c r="F237" s="54"/>
       <c r="G237" s="54"/>
       <c r="H237" s="54"/>
-      <c r="I237" s="145"/>
+      <c r="I237" s="121"/>
       <c r="J237" s="54"/>
       <c r="K237" s="54"/>
       <c r="L237" s="54"/>
@@ -22163,7 +23715,7 @@
       <c r="F238" s="54"/>
       <c r="G238" s="54"/>
       <c r="H238" s="54"/>
-      <c r="I238" s="145"/>
+      <c r="I238" s="121"/>
       <c r="J238" s="54"/>
       <c r="K238" s="54"/>
       <c r="L238" s="54"/>
@@ -22179,7 +23731,7 @@
       <c r="F239" s="54"/>
       <c r="G239" s="54"/>
       <c r="H239" s="54"/>
-      <c r="I239" s="145"/>
+      <c r="I239" s="121"/>
       <c r="J239" s="54"/>
       <c r="K239" s="54"/>
       <c r="L239" s="54"/>
@@ -22195,7 +23747,7 @@
       <c r="F240" s="54"/>
       <c r="G240" s="54"/>
       <c r="H240" s="54"/>
-      <c r="I240" s="145"/>
+      <c r="I240" s="121"/>
       <c r="J240" s="54"/>
       <c r="K240" s="54"/>
       <c r="L240" s="54"/>
@@ -22211,7 +23763,7 @@
       <c r="F241" s="54"/>
       <c r="G241" s="54"/>
       <c r="H241" s="54"/>
-      <c r="I241" s="145"/>
+      <c r="I241" s="121"/>
       <c r="J241" s="54"/>
       <c r="K241" s="54"/>
       <c r="L241" s="54"/>
@@ -22227,7 +23779,7 @@
       <c r="F242" s="54"/>
       <c r="G242" s="54"/>
       <c r="H242" s="54"/>
-      <c r="I242" s="145"/>
+      <c r="I242" s="121"/>
       <c r="J242" s="54"/>
       <c r="K242" s="54"/>
       <c r="L242" s="54"/>
@@ -22243,7 +23795,7 @@
       <c r="F243" s="54"/>
       <c r="G243" s="54"/>
       <c r="H243" s="54"/>
-      <c r="I243" s="145"/>
+      <c r="I243" s="121"/>
       <c r="J243" s="54"/>
       <c r="K243" s="54"/>
       <c r="L243" s="54"/>
@@ -22259,7 +23811,7 @@
       <c r="F244" s="54"/>
       <c r="G244" s="54"/>
       <c r="H244" s="54"/>
-      <c r="I244" s="145"/>
+      <c r="I244" s="121"/>
       <c r="J244" s="54"/>
       <c r="K244" s="54"/>
       <c r="L244" s="54"/>
@@ -22275,7 +23827,7 @@
       <c r="F245" s="54"/>
       <c r="G245" s="54"/>
       <c r="H245" s="54"/>
-      <c r="I245" s="145"/>
+      <c r="I245" s="121"/>
       <c r="J245" s="54"/>
       <c r="K245" s="54"/>
       <c r="L245" s="54"/>
@@ -22291,7 +23843,7 @@
       <c r="F246" s="54"/>
       <c r="G246" s="54"/>
       <c r="H246" s="54"/>
-      <c r="I246" s="145"/>
+      <c r="I246" s="121"/>
       <c r="J246" s="54"/>
       <c r="K246" s="54"/>
       <c r="L246" s="54"/>
@@ -22307,7 +23859,7 @@
       <c r="F247" s="54"/>
       <c r="G247" s="54"/>
       <c r="H247" s="54"/>
-      <c r="I247" s="145"/>
+      <c r="I247" s="121"/>
       <c r="J247" s="54"/>
       <c r="K247" s="54"/>
       <c r="L247" s="54"/>
@@ -22323,7 +23875,7 @@
       <c r="F248" s="54"/>
       <c r="G248" s="54"/>
       <c r="H248" s="54"/>
-      <c r="I248" s="145"/>
+      <c r="I248" s="121"/>
       <c r="J248" s="54"/>
       <c r="K248" s="54"/>
       <c r="L248" s="54"/>
@@ -22339,7 +23891,7 @@
       <c r="F249" s="54"/>
       <c r="G249" s="54"/>
       <c r="H249" s="54"/>
-      <c r="I249" s="145"/>
+      <c r="I249" s="121"/>
       <c r="J249" s="54"/>
       <c r="K249" s="54"/>
       <c r="L249" s="54"/>
@@ -22355,7 +23907,7 @@
       <c r="F250" s="54"/>
       <c r="G250" s="54"/>
       <c r="H250" s="54"/>
-      <c r="I250" s="145"/>
+      <c r="I250" s="121"/>
       <c r="J250" s="54"/>
       <c r="K250" s="54"/>
       <c r="L250" s="54"/>
@@ -22371,7 +23923,7 @@
       <c r="F251" s="54"/>
       <c r="G251" s="54"/>
       <c r="H251" s="54"/>
-      <c r="I251" s="145"/>
+      <c r="I251" s="121"/>
       <c r="J251" s="54"/>
       <c r="K251" s="54"/>
       <c r="L251" s="54"/>
@@ -22387,7 +23939,7 @@
       <c r="F252" s="54"/>
       <c r="G252" s="54"/>
       <c r="H252" s="54"/>
-      <c r="I252" s="145"/>
+      <c r="I252" s="121"/>
       <c r="J252" s="54"/>
       <c r="K252" s="54"/>
       <c r="L252" s="54"/>
@@ -22403,7 +23955,7 @@
       <c r="F253" s="54"/>
       <c r="G253" s="54"/>
       <c r="H253" s="54"/>
-      <c r="I253" s="145"/>
+      <c r="I253" s="121"/>
       <c r="J253" s="54"/>
       <c r="K253" s="54"/>
       <c r="L253" s="54"/>
@@ -22419,7 +23971,7 @@
       <c r="F254" s="54"/>
       <c r="G254" s="54"/>
       <c r="H254" s="54"/>
-      <c r="I254" s="145"/>
+      <c r="I254" s="121"/>
       <c r="J254" s="54"/>
       <c r="K254" s="54"/>
       <c r="L254" s="54"/>
@@ -22435,7 +23987,7 @@
       <c r="F255" s="54"/>
       <c r="G255" s="54"/>
       <c r="H255" s="54"/>
-      <c r="I255" s="145"/>
+      <c r="I255" s="121"/>
       <c r="J255" s="54"/>
       <c r="K255" s="54"/>
       <c r="L255" s="54"/>
@@ -22451,7 +24003,7 @@
       <c r="F256" s="54"/>
       <c r="G256" s="54"/>
       <c r="H256" s="54"/>
-      <c r="I256" s="145"/>
+      <c r="I256" s="121"/>
       <c r="J256" s="54"/>
       <c r="K256" s="54"/>
       <c r="L256" s="54"/>
@@ -22467,7 +24019,7 @@
       <c r="F257" s="54"/>
       <c r="G257" s="54"/>
       <c r="H257" s="54"/>
-      <c r="I257" s="145"/>
+      <c r="I257" s="121"/>
       <c r="J257" s="54"/>
       <c r="K257" s="54"/>
       <c r="L257" s="54"/>
@@ -22483,7 +24035,7 @@
       <c r="F258" s="54"/>
       <c r="G258" s="54"/>
       <c r="H258" s="54"/>
-      <c r="I258" s="145"/>
+      <c r="I258" s="121"/>
       <c r="J258" s="54"/>
       <c r="K258" s="54"/>
       <c r="L258" s="54"/>
@@ -22499,7 +24051,7 @@
       <c r="F259" s="54"/>
       <c r="G259" s="54"/>
       <c r="H259" s="54"/>
-      <c r="I259" s="145"/>
+      <c r="I259" s="121"/>
       <c r="J259" s="54"/>
       <c r="K259" s="54"/>
       <c r="L259" s="54"/>
@@ -22515,7 +24067,7 @@
       <c r="F260" s="54"/>
       <c r="G260" s="54"/>
       <c r="H260" s="54"/>
-      <c r="I260" s="145"/>
+      <c r="I260" s="121"/>
       <c r="J260" s="54"/>
       <c r="K260" s="54"/>
       <c r="L260" s="54"/>
@@ -22531,7 +24083,7 @@
       <c r="F261" s="54"/>
       <c r="G261" s="54"/>
       <c r="H261" s="54"/>
-      <c r="I261" s="145"/>
+      <c r="I261" s="121"/>
       <c r="J261" s="54"/>
       <c r="K261" s="54"/>
       <c r="L261" s="54"/>
@@ -22547,7 +24099,7 @@
       <c r="F262" s="54"/>
       <c r="G262" s="54"/>
       <c r="H262" s="54"/>
-      <c r="I262" s="145"/>
+      <c r="I262" s="121"/>
       <c r="J262" s="54"/>
       <c r="K262" s="54"/>
       <c r="L262" s="54"/>
@@ -22563,7 +24115,7 @@
       <c r="F263" s="54"/>
       <c r="G263" s="54"/>
       <c r="H263" s="54"/>
-      <c r="I263" s="145"/>
+      <c r="I263" s="121"/>
       <c r="J263" s="54"/>
       <c r="K263" s="54"/>
       <c r="L263" s="54"/>
@@ -22579,7 +24131,7 @@
       <c r="F264" s="54"/>
       <c r="G264" s="54"/>
       <c r="H264" s="54"/>
-      <c r="I264" s="145"/>
+      <c r="I264" s="121"/>
       <c r="J264" s="54"/>
       <c r="K264" s="54"/>
       <c r="L264" s="54"/>
@@ -22595,7 +24147,7 @@
       <c r="F265" s="54"/>
       <c r="G265" s="54"/>
       <c r="H265" s="54"/>
-      <c r="I265" s="145"/>
+      <c r="I265" s="121"/>
       <c r="J265" s="54"/>
       <c r="K265" s="54"/>
       <c r="L265" s="54"/>
@@ -22611,7 +24163,7 @@
       <c r="F266" s="54"/>
       <c r="G266" s="54"/>
       <c r="H266" s="54"/>
-      <c r="I266" s="145"/>
+      <c r="I266" s="121"/>
       <c r="J266" s="54"/>
       <c r="K266" s="54"/>
       <c r="L266" s="54"/>
@@ -22627,7 +24179,7 @@
       <c r="F267" s="54"/>
       <c r="G267" s="54"/>
       <c r="H267" s="54"/>
-      <c r="I267" s="145"/>
+      <c r="I267" s="121"/>
       <c r="J267" s="54"/>
       <c r="K267" s="54"/>
       <c r="L267" s="54"/>
@@ -22643,7 +24195,7 @@
       <c r="F268" s="54"/>
       <c r="G268" s="54"/>
       <c r="H268" s="54"/>
-      <c r="I268" s="145"/>
+      <c r="I268" s="121"/>
       <c r="J268" s="54"/>
       <c r="K268" s="54"/>
       <c r="L268" s="54"/>
@@ -22659,7 +24211,7 @@
       <c r="F269" s="54"/>
       <c r="G269" s="54"/>
       <c r="H269" s="54"/>
-      <c r="I269" s="145"/>
+      <c r="I269" s="121"/>
       <c r="J269" s="54"/>
       <c r="K269" s="54"/>
       <c r="L269" s="54"/>
@@ -22675,7 +24227,7 @@
       <c r="F270" s="54"/>
       <c r="G270" s="54"/>
       <c r="H270" s="54"/>
-      <c r="I270" s="145"/>
+      <c r="I270" s="121"/>
       <c r="J270" s="54"/>
       <c r="K270" s="54"/>
       <c r="L270" s="54"/>
@@ -22691,7 +24243,7 @@
       <c r="F271" s="54"/>
       <c r="G271" s="54"/>
       <c r="H271" s="54"/>
-      <c r="I271" s="145"/>
+      <c r="I271" s="121"/>
       <c r="J271" s="54"/>
       <c r="K271" s="54"/>
       <c r="L271" s="54"/>
@@ -22707,7 +24259,7 @@
       <c r="F272" s="54"/>
       <c r="G272" s="54"/>
       <c r="H272" s="54"/>
-      <c r="I272" s="145"/>
+      <c r="I272" s="121"/>
       <c r="J272" s="54"/>
       <c r="K272" s="54"/>
       <c r="L272" s="54"/>
@@ -22723,7 +24275,7 @@
       <c r="F273" s="54"/>
       <c r="G273" s="54"/>
       <c r="H273" s="54"/>
-      <c r="I273" s="145"/>
+      <c r="I273" s="121"/>
       <c r="J273" s="54"/>
       <c r="K273" s="54"/>
       <c r="L273" s="54"/>
@@ -22739,7 +24291,7 @@
       <c r="F274" s="54"/>
       <c r="G274" s="54"/>
       <c r="H274" s="54"/>
-      <c r="I274" s="145"/>
+      <c r="I274" s="121"/>
       <c r="J274" s="54"/>
       <c r="K274" s="54"/>
       <c r="L274" s="54"/>
@@ -22755,7 +24307,7 @@
       <c r="F275" s="54"/>
       <c r="G275" s="54"/>
       <c r="H275" s="54"/>
-      <c r="I275" s="145"/>
+      <c r="I275" s="121"/>
       <c r="J275" s="54"/>
       <c r="K275" s="54"/>
       <c r="L275" s="54"/>
@@ -22771,7 +24323,7 @@
       <c r="F276" s="54"/>
       <c r="G276" s="54"/>
       <c r="H276" s="54"/>
-      <c r="I276" s="145"/>
+      <c r="I276" s="121"/>
       <c r="J276" s="54"/>
       <c r="K276" s="54"/>
       <c r="L276" s="54"/>
@@ -22787,7 +24339,7 @@
       <c r="F277" s="54"/>
       <c r="G277" s="54"/>
       <c r="H277" s="54"/>
-      <c r="I277" s="145"/>
+      <c r="I277" s="121"/>
       <c r="J277" s="54"/>
       <c r="K277" s="54"/>
       <c r="L277" s="54"/>
@@ -22803,7 +24355,7 @@
       <c r="F278" s="54"/>
       <c r="G278" s="54"/>
       <c r="H278" s="54"/>
-      <c r="I278" s="145"/>
+      <c r="I278" s="121"/>
       <c r="J278" s="54"/>
       <c r="K278" s="54"/>
       <c r="L278" s="54"/>
@@ -22819,7 +24371,7 @@
       <c r="F279" s="54"/>
       <c r="G279" s="54"/>
       <c r="H279" s="54"/>
-      <c r="I279" s="145"/>
+      <c r="I279" s="121"/>
       <c r="J279" s="54"/>
       <c r="K279" s="54"/>
       <c r="L279" s="54"/>
@@ -22835,7 +24387,7 @@
       <c r="F280" s="54"/>
       <c r="G280" s="54"/>
       <c r="H280" s="54"/>
-      <c r="I280" s="145"/>
+      <c r="I280" s="121"/>
       <c r="J280" s="54"/>
       <c r="K280" s="54"/>
       <c r="L280" s="54"/>
@@ -22851,7 +24403,7 @@
       <c r="F281" s="54"/>
       <c r="G281" s="54"/>
       <c r="H281" s="54"/>
-      <c r="I281" s="145"/>
+      <c r="I281" s="121"/>
       <c r="J281" s="54"/>
       <c r="K281" s="54"/>
       <c r="L281" s="54"/>
@@ -22867,7 +24419,7 @@
       <c r="F282" s="54"/>
       <c r="G282" s="54"/>
       <c r="H282" s="54"/>
-      <c r="I282" s="145"/>
+      <c r="I282" s="121"/>
       <c r="J282" s="54"/>
       <c r="K282" s="54"/>
       <c r="L282" s="54"/>
@@ -22883,7 +24435,7 @@
       <c r="F283" s="54"/>
       <c r="G283" s="54"/>
       <c r="H283" s="54"/>
-      <c r="I283" s="145"/>
+      <c r="I283" s="121"/>
       <c r="J283" s="54"/>
       <c r="K283" s="54"/>
       <c r="L283" s="54"/>
@@ -22899,7 +24451,7 @@
       <c r="F284" s="54"/>
       <c r="G284" s="54"/>
       <c r="H284" s="54"/>
-      <c r="I284" s="145"/>
+      <c r="I284" s="121"/>
       <c r="J284" s="54"/>
       <c r="K284" s="54"/>
       <c r="L284" s="54"/>
@@ -22915,7 +24467,7 @@
       <c r="F285" s="54"/>
       <c r="G285" s="54"/>
       <c r="H285" s="54"/>
-      <c r="I285" s="145"/>
+      <c r="I285" s="121"/>
       <c r="J285" s="54"/>
       <c r="K285" s="54"/>
       <c r="L285" s="54"/>
@@ -22931,7 +24483,7 @@
       <c r="F286" s="54"/>
       <c r="G286" s="54"/>
       <c r="H286" s="54"/>
-      <c r="I286" s="145"/>
+      <c r="I286" s="121"/>
       <c r="J286" s="54"/>
       <c r="K286" s="54"/>
       <c r="L286" s="54"/>
@@ -22947,7 +24499,7 @@
       <c r="F287" s="54"/>
       <c r="G287" s="54"/>
       <c r="H287" s="54"/>
-      <c r="I287" s="145"/>
+      <c r="I287" s="121"/>
       <c r="J287" s="54"/>
       <c r="K287" s="54"/>
       <c r="L287" s="54"/>
@@ -22963,7 +24515,7 @@
       <c r="F288" s="54"/>
       <c r="G288" s="54"/>
       <c r="H288" s="54"/>
-      <c r="I288" s="145"/>
+      <c r="I288" s="121"/>
       <c r="J288" s="54"/>
       <c r="K288" s="54"/>
       <c r="L288" s="54"/>
@@ -22979,7 +24531,7 @@
       <c r="F289" s="54"/>
       <c r="G289" s="54"/>
       <c r="H289" s="54"/>
-      <c r="I289" s="145"/>
+      <c r="I289" s="121"/>
       <c r="J289" s="54"/>
       <c r="K289" s="54"/>
       <c r="L289" s="54"/>
@@ -22995,7 +24547,7 @@
       <c r="F290" s="54"/>
       <c r="G290" s="54"/>
       <c r="H290" s="54"/>
-      <c r="I290" s="145"/>
+      <c r="I290" s="121"/>
       <c r="J290" s="54"/>
       <c r="K290" s="54"/>
       <c r="L290" s="54"/>
@@ -23011,7 +24563,7 @@
       <c r="F291" s="54"/>
       <c r="G291" s="54"/>
       <c r="H291" s="54"/>
-      <c r="I291" s="145"/>
+      <c r="I291" s="121"/>
       <c r="J291" s="54"/>
       <c r="K291" s="54"/>
       <c r="L291" s="54"/>
@@ -23027,7 +24579,7 @@
       <c r="F292" s="54"/>
       <c r="G292" s="54"/>
       <c r="H292" s="54"/>
-      <c r="I292" s="145"/>
+      <c r="I292" s="121"/>
       <c r="J292" s="54"/>
       <c r="K292" s="54"/>
       <c r="L292" s="54"/>
@@ -23043,7 +24595,7 @@
       <c r="F293" s="54"/>
       <c r="G293" s="54"/>
       <c r="H293" s="54"/>
-      <c r="I293" s="145"/>
+      <c r="I293" s="121"/>
       <c r="J293" s="54"/>
       <c r="K293" s="54"/>
       <c r="L293" s="54"/>
@@ -23059,7 +24611,7 @@
       <c r="F294" s="54"/>
       <c r="G294" s="54"/>
       <c r="H294" s="54"/>
-      <c r="I294" s="145"/>
+      <c r="I294" s="121"/>
       <c r="J294" s="54"/>
       <c r="K294" s="54"/>
       <c r="L294" s="54"/>
@@ -23075,7 +24627,7 @@
       <c r="F295" s="54"/>
       <c r="G295" s="54"/>
       <c r="H295" s="54"/>
-      <c r="I295" s="145"/>
+      <c r="I295" s="121"/>
       <c r="J295" s="54"/>
       <c r="K295" s="54"/>
       <c r="L295" s="54"/>
@@ -23091,7 +24643,7 @@
       <c r="F296" s="54"/>
       <c r="G296" s="54"/>
       <c r="H296" s="54"/>
-      <c r="I296" s="145"/>
+      <c r="I296" s="121"/>
       <c r="J296" s="54"/>
       <c r="K296" s="54"/>
       <c r="L296" s="54"/>
@@ -23107,7 +24659,7 @@
       <c r="F297" s="54"/>
       <c r="G297" s="54"/>
       <c r="H297" s="54"/>
-      <c r="I297" s="145"/>
+      <c r="I297" s="121"/>
       <c r="J297" s="54"/>
       <c r="K297" s="54"/>
       <c r="L297" s="54"/>
@@ -23123,7 +24675,7 @@
       <c r="F298" s="54"/>
       <c r="G298" s="54"/>
       <c r="H298" s="54"/>
-      <c r="I298" s="145"/>
+      <c r="I298" s="121"/>
       <c r="J298" s="54"/>
       <c r="K298" s="54"/>
       <c r="L298" s="54"/>
@@ -23139,7 +24691,7 @@
       <c r="F299" s="54"/>
       <c r="G299" s="54"/>
       <c r="H299" s="54"/>
-      <c r="I299" s="145"/>
+      <c r="I299" s="121"/>
       <c r="J299" s="54"/>
       <c r="K299" s="54"/>
       <c r="L299" s="54"/>
@@ -23155,7 +24707,7 @@
       <c r="F300" s="54"/>
       <c r="G300" s="54"/>
       <c r="H300" s="54"/>
-      <c r="I300" s="145"/>
+      <c r="I300" s="121"/>
       <c r="J300" s="54"/>
       <c r="K300" s="54"/>
       <c r="L300" s="54"/>
@@ -23171,7 +24723,7 @@
       <c r="F301" s="54"/>
       <c r="G301" s="54"/>
       <c r="H301" s="54"/>
-      <c r="I301" s="145"/>
+      <c r="I301" s="121"/>
       <c r="J301" s="54"/>
       <c r="K301" s="54"/>
       <c r="L301" s="54"/>
@@ -23187,7 +24739,7 @@
       <c r="F302" s="54"/>
       <c r="G302" s="54"/>
       <c r="H302" s="54"/>
-      <c r="I302" s="145"/>
+      <c r="I302" s="121"/>
       <c r="J302" s="54"/>
       <c r="K302" s="54"/>
       <c r="L302" s="54"/>
@@ -23203,7 +24755,7 @@
       <c r="F303" s="54"/>
       <c r="G303" s="54"/>
       <c r="H303" s="54"/>
-      <c r="I303" s="145"/>
+      <c r="I303" s="121"/>
       <c r="J303" s="54"/>
       <c r="K303" s="54"/>
       <c r="L303" s="54"/>
@@ -23219,7 +24771,7 @@
       <c r="F304" s="54"/>
       <c r="G304" s="54"/>
       <c r="H304" s="54"/>
-      <c r="I304" s="145"/>
+      <c r="I304" s="121"/>
       <c r="J304" s="54"/>
       <c r="K304" s="54"/>
       <c r="L304" s="54"/>
@@ -23235,7 +24787,7 @@
       <c r="F305" s="54"/>
       <c r="G305" s="54"/>
       <c r="H305" s="54"/>
-      <c r="I305" s="145"/>
+      <c r="I305" s="121"/>
       <c r="J305" s="54"/>
       <c r="K305" s="54"/>
       <c r="L305" s="54"/>
@@ -23251,7 +24803,7 @@
       <c r="F306" s="54"/>
       <c r="G306" s="54"/>
       <c r="H306" s="54"/>
-      <c r="I306" s="145"/>
+      <c r="I306" s="121"/>
       <c r="J306" s="54"/>
       <c r="K306" s="54"/>
       <c r="L306" s="54"/>
@@ -23267,7 +24819,7 @@
       <c r="F307" s="54"/>
       <c r="G307" s="54"/>
       <c r="H307" s="54"/>
-      <c r="I307" s="145"/>
+      <c r="I307" s="121"/>
       <c r="J307" s="54"/>
       <c r="K307" s="54"/>
       <c r="L307" s="54"/>
@@ -23283,7 +24835,7 @@
       <c r="F308" s="54"/>
       <c r="G308" s="54"/>
       <c r="H308" s="54"/>
-      <c r="I308" s="145"/>
+      <c r="I308" s="121"/>
       <c r="J308" s="54"/>
       <c r="K308" s="54"/>
       <c r="L308" s="54"/>
@@ -23299,7 +24851,7 @@
       <c r="F309" s="54"/>
       <c r="G309" s="54"/>
       <c r="H309" s="54"/>
-      <c r="I309" s="145"/>
+      <c r="I309" s="121"/>
       <c r="J309" s="54"/>
       <c r="K309" s="54"/>
       <c r="L309" s="54"/>
@@ -23315,7 +24867,7 @@
       <c r="F310" s="54"/>
       <c r="G310" s="54"/>
       <c r="H310" s="54"/>
-      <c r="I310" s="145"/>
+      <c r="I310" s="121"/>
       <c r="J310" s="54"/>
       <c r="K310" s="54"/>
       <c r="L310" s="54"/>
@@ -23331,7 +24883,7 @@
       <c r="F311" s="54"/>
       <c r="G311" s="54"/>
       <c r="H311" s="54"/>
-      <c r="I311" s="145"/>
+      <c r="I311" s="121"/>
       <c r="J311" s="54"/>
       <c r="K311" s="54"/>
       <c r="L311" s="54"/>
@@ -23347,7 +24899,7 @@
       <c r="F312" s="54"/>
       <c r="G312" s="54"/>
       <c r="H312" s="54"/>
-      <c r="I312" s="145"/>
+      <c r="I312" s="121"/>
       <c r="J312" s="54"/>
       <c r="K312" s="54"/>
       <c r="L312" s="54"/>
@@ -23363,7 +24915,7 @@
       <c r="F313" s="54"/>
       <c r="G313" s="54"/>
       <c r="H313" s="54"/>
-      <c r="I313" s="145"/>
+      <c r="I313" s="121"/>
       <c r="J313" s="54"/>
       <c r="K313" s="54"/>
       <c r="L313" s="54"/>
@@ -23379,7 +24931,7 @@
       <c r="F314" s="54"/>
       <c r="G314" s="54"/>
       <c r="H314" s="54"/>
-      <c r="I314" s="145"/>
+      <c r="I314" s="121"/>
       <c r="J314" s="54"/>
       <c r="K314" s="54"/>
       <c r="L314" s="54"/>
@@ -23395,7 +24947,7 @@
       <c r="F315" s="54"/>
       <c r="G315" s="54"/>
       <c r="H315" s="54"/>
-      <c r="I315" s="145"/>
+      <c r="I315" s="121"/>
       <c r="J315" s="54"/>
       <c r="K315" s="54"/>
       <c r="L315" s="54"/>
@@ -23411,7 +24963,7 @@
       <c r="F316" s="54"/>
       <c r="G316" s="54"/>
       <c r="H316" s="54"/>
-      <c r="I316" s="145"/>
+      <c r="I316" s="121"/>
       <c r="J316" s="54"/>
       <c r="K316" s="54"/>
       <c r="L316" s="54"/>
@@ -23427,7 +24979,7 @@
       <c r="F317" s="54"/>
       <c r="G317" s="54"/>
       <c r="H317" s="54"/>
-      <c r="I317" s="145"/>
+      <c r="I317" s="121"/>
       <c r="J317" s="54"/>
       <c r="K317" s="54"/>
       <c r="L317" s="54"/>
@@ -23443,7 +24995,7 @@
       <c r="F318" s="54"/>
       <c r="G318" s="54"/>
       <c r="H318" s="54"/>
-      <c r="I318" s="145"/>
+      <c r="I318" s="121"/>
       <c r="J318" s="54"/>
       <c r="K318" s="54"/>
       <c r="L318" s="54"/>
@@ -23459,7 +25011,7 @@
       <c r="F319" s="54"/>
       <c r="G319" s="54"/>
       <c r="H319" s="54"/>
-      <c r="I319" s="145"/>
+      <c r="I319" s="121"/>
       <c r="J319" s="54"/>
       <c r="K319" s="54"/>
       <c r="L319" s="54"/>
@@ -23475,7 +25027,7 @@
       <c r="F320" s="54"/>
       <c r="G320" s="54"/>
       <c r="H320" s="54"/>
-      <c r="I320" s="145"/>
+      <c r="I320" s="121"/>
       <c r="J320" s="54"/>
       <c r="K320" s="54"/>
       <c r="L320" s="54"/>
@@ -23491,7 +25043,7 @@
       <c r="F321" s="54"/>
       <c r="G321" s="54"/>
       <c r="H321" s="54"/>
-      <c r="I321" s="145"/>
+      <c r="I321" s="121"/>
       <c r="J321" s="54"/>
       <c r="K321" s="54"/>
       <c r="L321" s="54"/>
@@ -23507,7 +25059,7 @@
       <c r="F322" s="54"/>
       <c r="G322" s="54"/>
       <c r="H322" s="54"/>
-      <c r="I322" s="145"/>
+      <c r="I322" s="121"/>
       <c r="J322" s="54"/>
       <c r="K322" s="54"/>
       <c r="L322" s="54"/>
@@ -23523,7 +25075,7 @@
       <c r="F323" s="54"/>
       <c r="G323" s="54"/>
       <c r="H323" s="54"/>
-      <c r="I323" s="145"/>
+      <c r="I323" s="121"/>
       <c r="J323" s="54"/>
       <c r="K323" s="54"/>
       <c r="L323" s="54"/>
@@ -23539,7 +25091,7 @@
       <c r="F324" s="54"/>
       <c r="G324" s="54"/>
       <c r="H324" s="54"/>
-      <c r="I324" s="145"/>
+      <c r="I324" s="121"/>
       <c r="J324" s="54"/>
       <c r="K324" s="54"/>
       <c r="L324" s="54"/>
@@ -23555,7 +25107,7 @@
       <c r="F325" s="54"/>
       <c r="G325" s="54"/>
       <c r="H325" s="54"/>
-      <c r="I325" s="145"/>
+      <c r="I325" s="121"/>
       <c r="J325" s="54"/>
       <c r="K325" s="54"/>
       <c r="L325" s="54"/>
@@ -23571,7 +25123,7 @@
       <c r="F326" s="54"/>
       <c r="G326" s="54"/>
       <c r="H326" s="54"/>
-      <c r="I326" s="145"/>
+      <c r="I326" s="121"/>
       <c r="J326" s="54"/>
       <c r="K326" s="54"/>
       <c r="L326" s="54"/>
@@ -23587,7 +25139,7 @@
       <c r="F327" s="54"/>
       <c r="G327" s="54"/>
       <c r="H327" s="54"/>
-      <c r="I327" s="145"/>
+      <c r="I327" s="121"/>
       <c r="J327" s="54"/>
       <c r="K327" s="54"/>
       <c r="L327" s="54"/>
@@ -23603,7 +25155,7 @@
       <c r="F328" s="54"/>
       <c r="G328" s="54"/>
       <c r="H328" s="54"/>
-      <c r="I328" s="145"/>
+      <c r="I328" s="121"/>
       <c r="J328" s="54"/>
       <c r="K328" s="54"/>
       <c r="L328" s="54"/>
@@ -23619,7 +25171,7 @@
       <c r="F329" s="54"/>
       <c r="G329" s="54"/>
       <c r="H329" s="54"/>
-      <c r="I329" s="145"/>
+      <c r="I329" s="121"/>
       <c r="J329" s="54"/>
       <c r="K329" s="54"/>
       <c r="L329" s="54"/>
@@ -23635,7 +25187,7 @@
       <c r="F330" s="54"/>
       <c r="G330" s="54"/>
       <c r="H330" s="54"/>
-      <c r="I330" s="145"/>
+      <c r="I330" s="121"/>
       <c r="J330" s="54"/>
       <c r="K330" s="54"/>
       <c r="L330" s="54"/>
@@ -23651,7 +25203,7 @@
       <c r="F331" s="54"/>
       <c r="G331" s="54"/>
       <c r="H331" s="54"/>
-      <c r="I331" s="145"/>
+      <c r="I331" s="121"/>
       <c r="J331" s="54"/>
       <c r="K331" s="54"/>
       <c r="L331" s="54"/>
@@ -23667,7 +25219,7 @@
       <c r="F332" s="54"/>
       <c r="G332" s="54"/>
       <c r="H332" s="54"/>
-      <c r="I332" s="145"/>
+      <c r="I332" s="121"/>
       <c r="J332" s="54"/>
       <c r="K332" s="54"/>
       <c r="L332" s="54"/>
@@ -23683,7 +25235,7 @@
       <c r="F333" s="54"/>
       <c r="G333" s="54"/>
       <c r="H333" s="54"/>
-      <c r="I333" s="145"/>
+      <c r="I333" s="121"/>
       <c r="J333" s="54"/>
       <c r="K333" s="54"/>
       <c r="L333" s="54"/>
@@ -23699,7 +25251,7 @@
       <c r="F334" s="54"/>
       <c r="G334" s="54"/>
       <c r="H334" s="54"/>
-      <c r="I334" s="145"/>
+      <c r="I334" s="121"/>
       <c r="J334" s="54"/>
       <c r="K334" s="54"/>
       <c r="L334" s="54"/>
@@ -23715,7 +25267,7 @@
       <c r="F335" s="54"/>
       <c r="G335" s="54"/>
       <c r="H335" s="54"/>
-      <c r="I335" s="145"/>
+      <c r="I335" s="121"/>
       <c r="J335" s="54"/>
       <c r="K335" s="54"/>
       <c r="L335" s="54"/>
@@ -23731,7 +25283,7 @@
       <c r="F336" s="54"/>
       <c r="G336" s="54"/>
       <c r="H336" s="54"/>
-      <c r="I336" s="145"/>
+      <c r="I336" s="121"/>
       <c r="J336" s="54"/>
       <c r="K336" s="54"/>
       <c r="L336" s="54"/>
@@ -23747,7 +25299,7 @@
       <c r="F337" s="54"/>
       <c r="G337" s="54"/>
       <c r="H337" s="54"/>
-      <c r="I337" s="145"/>
+      <c r="I337" s="121"/>
       <c r="J337" s="54"/>
       <c r="K337" s="54"/>
       <c r="L337" s="54"/>
@@ -23763,7 +25315,7 @@
       <c r="F338" s="54"/>
       <c r="G338" s="54"/>
       <c r="H338" s="54"/>
-      <c r="I338" s="145"/>
+      <c r="I338" s="121"/>
       <c r="J338" s="54"/>
       <c r="K338" s="54"/>
       <c r="L338" s="54"/>
@@ -23779,7 +25331,7 @@
       <c r="F339" s="54"/>
       <c r="G339" s="54"/>
       <c r="H339" s="54"/>
-      <c r="I339" s="145"/>
+      <c r="I339" s="121"/>
       <c r="J339" s="54"/>
       <c r="K339" s="54"/>
       <c r="L339" s="54"/>
@@ -23795,7 +25347,7 @@
       <c r="F340" s="54"/>
       <c r="G340" s="54"/>
       <c r="H340" s="54"/>
-      <c r="I340" s="145"/>
+      <c r="I340" s="121"/>
       <c r="J340" s="54"/>
       <c r="K340" s="54"/>
       <c r="L340" s="54"/>
@@ -23811,7 +25363,7 @@
       <c r="F341" s="54"/>
       <c r="G341" s="54"/>
       <c r="H341" s="54"/>
-      <c r="I341" s="145"/>
+      <c r="I341" s="121"/>
       <c r="J341" s="54"/>
       <c r="K341" s="54"/>
       <c r="L341" s="54"/>
@@ -23827,7 +25379,7 @@
       <c r="F342" s="54"/>
       <c r="G342" s="54"/>
       <c r="H342" s="54"/>
-      <c r="I342" s="145"/>
+      <c r="I342" s="121"/>
       <c r="J342" s="54"/>
       <c r="K342" s="54"/>
       <c r="L342" s="54"/>
@@ -23843,7 +25395,7 @@
       <c r="F343" s="54"/>
       <c r="G343" s="54"/>
       <c r="H343" s="54"/>
-      <c r="I343" s="145"/>
+      <c r="I343" s="121"/>
       <c r="J343" s="54"/>
       <c r="K343" s="54"/>
       <c r="L343" s="54"/>
@@ -23859,7 +25411,7 @@
       <c r="F344" s="54"/>
       <c r="G344" s="54"/>
       <c r="H344" s="54"/>
-      <c r="I344" s="145"/>
+      <c r="I344" s="121"/>
       <c r="J344" s="54"/>
       <c r="K344" s="54"/>
       <c r="L344" s="54"/>
@@ -23875,7 +25427,7 @@
       <c r="F345" s="54"/>
       <c r="G345" s="54"/>
       <c r="H345" s="54"/>
-      <c r="I345" s="145"/>
+      <c r="I345" s="121"/>
       <c r="J345" s="54"/>
       <c r="K345" s="54"/>
       <c r="L345" s="54"/>
@@ -23891,7 +25443,7 @@
       <c r="F346" s="54"/>
       <c r="G346" s="54"/>
       <c r="H346" s="54"/>
-      <c r="I346" s="145"/>
+      <c r="I346" s="121"/>
       <c r="J346" s="54"/>
       <c r="K346" s="54"/>
       <c r="L346" s="54"/>
@@ -23907,7 +25459,7 @@
       <c r="F347" s="54"/>
       <c r="G347" s="54"/>
       <c r="H347" s="54"/>
-      <c r="I347" s="145"/>
+      <c r="I347" s="121"/>
       <c r="J347" s="54"/>
       <c r="K347" s="54"/>
       <c r="L347" s="54"/>
@@ -23923,7 +25475,7 @@
       <c r="F348" s="54"/>
       <c r="G348" s="54"/>
       <c r="H348" s="54"/>
-      <c r="I348" s="145"/>
+      <c r="I348" s="121"/>
       <c r="J348" s="54"/>
       <c r="K348" s="54"/>
       <c r="L348" s="54"/>
@@ -23939,7 +25491,7 @@
       <c r="F349" s="54"/>
       <c r="G349" s="54"/>
       <c r="H349" s="54"/>
-      <c r="I349" s="145"/>
+      <c r="I349" s="121"/>
       <c r="J349" s="54"/>
       <c r="K349" s="54"/>
       <c r="L349" s="54"/>
@@ -23955,7 +25507,7 @@
       <c r="F350" s="54"/>
       <c r="G350" s="54"/>
       <c r="H350" s="54"/>
-      <c r="I350" s="145"/>
+      <c r="I350" s="121"/>
       <c r="J350" s="54"/>
       <c r="K350" s="54"/>
       <c r="L350" s="54"/>
@@ -23971,7 +25523,7 @@
       <c r="F351" s="54"/>
       <c r="G351" s="54"/>
       <c r="H351" s="54"/>
-      <c r="I351" s="145"/>
+      <c r="I351" s="121"/>
       <c r="J351" s="54"/>
       <c r="K351" s="54"/>
       <c r="L351" s="54"/>
@@ -23987,7 +25539,7 @@
       <c r="F352" s="54"/>
       <c r="G352" s="54"/>
       <c r="H352" s="54"/>
-      <c r="I352" s="145"/>
+      <c r="I352" s="121"/>
       <c r="J352" s="54"/>
       <c r="K352" s="54"/>
       <c r="L352" s="54"/>
@@ -24003,7 +25555,7 @@
       <c r="F353" s="54"/>
       <c r="G353" s="54"/>
       <c r="H353" s="54"/>
-      <c r="I353" s="145"/>
+      <c r="I353" s="121"/>
       <c r="J353" s="54"/>
       <c r="K353" s="54"/>
       <c r="L353" s="54"/>
@@ -24019,7 +25571,7 @@
       <c r="F354" s="54"/>
       <c r="G354" s="54"/>
       <c r="H354" s="54"/>
-      <c r="I354" s="145"/>
+      <c r="I354" s="121"/>
       <c r="J354" s="54"/>
       <c r="K354" s="54"/>
       <c r="L354" s="54"/>
@@ -24035,7 +25587,7 @@
       <c r="F355" s="54"/>
       <c r="G355" s="54"/>
       <c r="H355" s="54"/>
-      <c r="I355" s="145"/>
+      <c r="I355" s="121"/>
       <c r="J355" s="54"/>
       <c r="K355" s="54"/>
       <c r="L355" s="54"/>
@@ -24051,7 +25603,7 @@
       <c r="F356" s="54"/>
       <c r="G356" s="54"/>
       <c r="H356" s="54"/>
-      <c r="I356" s="145"/>
+      <c r="I356" s="121"/>
       <c r="J356" s="54"/>
       <c r="K356" s="54"/>
       <c r="L356" s="54"/>
@@ -24067,7 +25619,7 @@
       <c r="F357" s="54"/>
       <c r="G357" s="54"/>
       <c r="H357" s="54"/>
-      <c r="I357" s="145"/>
+      <c r="I357" s="121"/>
       <c r="J357" s="54"/>
       <c r="K357" s="54"/>
       <c r="L357" s="54"/>
@@ -24083,7 +25635,7 @@
       <c r="F358" s="54"/>
       <c r="G358" s="54"/>
       <c r="H358" s="54"/>
-      <c r="I358" s="145"/>
+      <c r="I358" s="121"/>
       <c r="J358" s="54"/>
       <c r="K358" s="54"/>
       <c r="L358" s="54"/>
@@ -24099,7 +25651,7 @@
       <c r="F359" s="54"/>
       <c r="G359" s="54"/>
       <c r="H359" s="54"/>
-      <c r="I359" s="145"/>
+      <c r="I359" s="121"/>
       <c r="J359" s="54"/>
       <c r="K359" s="54"/>
       <c r="L359" s="54"/>
@@ -24115,7 +25667,7 @@
       <c r="F360" s="54"/>
       <c r="G360" s="54"/>
       <c r="H360" s="54"/>
-      <c r="I360" s="145"/>
+      <c r="I360" s="121"/>
       <c r="J360" s="54"/>
       <c r="K360" s="54"/>
       <c r="L360" s="54"/>
@@ -24131,7 +25683,7 @@
       <c r="F361" s="54"/>
       <c r="G361" s="54"/>
       <c r="H361" s="54"/>
-      <c r="I361" s="145"/>
+      <c r="I361" s="121"/>
       <c r="J361" s="54"/>
       <c r="K361" s="54"/>
       <c r="L361" s="54"/>
@@ -24147,7 +25699,7 @@
       <c r="F362" s="54"/>
       <c r="G362" s="54"/>
       <c r="H362" s="54"/>
-      <c r="I362" s="145"/>
+      <c r="I362" s="121"/>
       <c r="J362" s="54"/>
       <c r="K362" s="54"/>
       <c r="L362" s="54"/>
@@ -24163,7 +25715,7 @@
       <c r="F363" s="54"/>
       <c r="G363" s="54"/>
       <c r="H363" s="54"/>
-      <c r="I363" s="145"/>
+      <c r="I363" s="121"/>
       <c r="J363" s="54"/>
       <c r="K363" s="54"/>
       <c r="L363" s="54"/>
@@ -24179,7 +25731,7 @@
       <c r="F364" s="54"/>
       <c r="G364" s="54"/>
       <c r="H364" s="54"/>
-      <c r="I364" s="145"/>
+      <c r="I364" s="121"/>
       <c r="J364" s="54"/>
       <c r="K364" s="54"/>
       <c r="L364" s="54"/>
@@ -24195,7 +25747,7 @@
       <c r="F365" s="54"/>
       <c r="G365" s="54"/>
       <c r="H365" s="54"/>
-      <c r="I365" s="145"/>
+      <c r="I365" s="121"/>
       <c r="J365" s="54"/>
       <c r="K365" s="54"/>
       <c r="L365" s="54"/>
@@ -24211,7 +25763,7 @@
       <c r="F366" s="54"/>
       <c r="G366" s="54"/>
       <c r="H366" s="54"/>
-      <c r="I366" s="145"/>
+      <c r="I366" s="121"/>
       <c r="J366" s="54"/>
       <c r="K366" s="54"/>
       <c r="L366" s="54"/>
@@ -24227,7 +25779,7 @@
       <c r="F367" s="54"/>
       <c r="G367" s="54"/>
       <c r="H367" s="54"/>
-      <c r="I367" s="145"/>
+      <c r="I367" s="121"/>
       <c r="J367" s="54"/>
       <c r="K367" s="54"/>
       <c r="L367" s="54"/>
@@ -24243,7 +25795,7 @@
       <c r="F368" s="54"/>
       <c r="G368" s="54"/>
       <c r="H368" s="54"/>
-      <c r="I368" s="145"/>
+      <c r="I368" s="121"/>
       <c r="J368" s="54"/>
       <c r="K368" s="54"/>
       <c r="L368" s="54"/>
@@ -24259,7 +25811,7 @@
       <c r="F369" s="54"/>
       <c r="G369" s="54"/>
       <c r="H369" s="54"/>
-      <c r="I369" s="145"/>
+      <c r="I369" s="121"/>
       <c r="J369" s="54"/>
       <c r="K369" s="54"/>
       <c r="L369" s="54"/>
@@ -24275,7 +25827,7 @@
       <c r="F370" s="54"/>
       <c r="G370" s="54"/>
       <c r="H370" s="54"/>
-      <c r="I370" s="145"/>
+      <c r="I370" s="121"/>
       <c r="J370" s="54"/>
       <c r="K370" s="54"/>
       <c r="L370" s="54"/>
@@ -24291,7 +25843,7 @@
       <c r="F371" s="54"/>
       <c r="G371" s="54"/>
       <c r="H371" s="54"/>
-      <c r="I371" s="145"/>
+      <c r="I371" s="121"/>
       <c r="J371" s="54"/>
       <c r="K371" s="54"/>
       <c r="L371" s="54"/>
@@ -24307,7 +25859,7 @@
       <c r="F372" s="54"/>
       <c r="G372" s="54"/>
       <c r="H372" s="54"/>
-      <c r="I372" s="145"/>
+      <c r="I372" s="121"/>
       <c r="J372" s="54"/>
       <c r="K372" s="54"/>
       <c r="L372" s="54"/>
@@ -24323,7 +25875,7 @@
       <c r="F373" s="54"/>
       <c r="G373" s="54"/>
       <c r="H373" s="54"/>
-      <c r="I373" s="145"/>
+      <c r="I373" s="121"/>
       <c r="J373" s="54"/>
       <c r="K373" s="54"/>
       <c r="L373" s="54"/>
@@ -24339,7 +25891,7 @@
       <c r="F374" s="54"/>
       <c r="G374" s="54"/>
       <c r="H374" s="54"/>
-      <c r="I374" s="145"/>
+      <c r="I374" s="121"/>
       <c r="J374" s="54"/>
       <c r="K374" s="54"/>
       <c r="L374" s="54"/>
@@ -24355,7 +25907,7 @@
       <c r="F375" s="54"/>
       <c r="G375" s="54"/>
       <c r="H375" s="54"/>
-      <c r="I375" s="145"/>
+      <c r="I375" s="121"/>
       <c r="J375" s="54"/>
       <c r="K375" s="54"/>
       <c r="L375" s="54"/>
@@ -24371,7 +25923,7 @@
       <c r="F376" s="54"/>
       <c r="G376" s="54"/>
       <c r="H376" s="54"/>
-      <c r="I376" s="145"/>
+      <c r="I376" s="121"/>
       <c r="J376" s="54"/>
       <c r="K376" s="54"/>
       <c r="L376" s="54"/>
@@ -24387,7 +25939,7 @@
       <c r="F377" s="54"/>
       <c r="G377" s="54"/>
       <c r="H377" s="54"/>
-      <c r="I377" s="145"/>
+      <c r="I377" s="121"/>
       <c r="J377" s="54"/>
       <c r="K377" s="54"/>
       <c r="L377" s="54"/>
@@ -24403,7 +25955,7 @@
       <c r="F378" s="54"/>
       <c r="G378" s="54"/>
       <c r="H378" s="54"/>
-      <c r="I378" s="145"/>
+      <c r="I378" s="121"/>
       <c r="J378" s="54"/>
       <c r="K378" s="54"/>
       <c r="L378" s="54"/>
@@ -24419,7 +25971,7 @@
       <c r="F379" s="54"/>
       <c r="G379" s="54"/>
       <c r="H379" s="54"/>
-      <c r="I379" s="145"/>
+      <c r="I379" s="121"/>
       <c r="J379" s="54"/>
       <c r="K379" s="54"/>
       <c r="L379" s="54"/>
@@ -24435,7 +25987,7 @@
       <c r="F380" s="54"/>
       <c r="G380" s="54"/>
       <c r="H380" s="54"/>
-      <c r="I380" s="145"/>
+      <c r="I380" s="121"/>
       <c r="J380" s="54"/>
       <c r="K380" s="54"/>
       <c r="L380" s="54"/>
@@ -24451,7 +26003,7 @@
       <c r="F381" s="54"/>
       <c r="G381" s="54"/>
       <c r="H381" s="54"/>
-      <c r="I381" s="145"/>
+      <c r="I381" s="121"/>
       <c r="J381" s="54"/>
       <c r="K381" s="54"/>
       <c r="L381" s="54"/>
@@ -24467,7 +26019,7 @@
       <c r="F382" s="54"/>
       <c r="G382" s="54"/>
       <c r="H382" s="54"/>
-      <c r="I382" s="145"/>
+      <c r="I382" s="121"/>
       <c r="J382" s="54"/>
       <c r="K382" s="54"/>
       <c r="L382" s="54"/>
@@ -24483,7 +26035,7 @@
       <c r="F383" s="54"/>
       <c r="G383" s="54"/>
       <c r="H383" s="54"/>
-      <c r="I383" s="145"/>
+      <c r="I383" s="121"/>
       <c r="J383" s="54"/>
       <c r="K383" s="54"/>
       <c r="L383" s="54"/>
@@ -24499,7 +26051,7 @@
       <c r="F384" s="54"/>
       <c r="G384" s="54"/>
       <c r="H384" s="54"/>
-      <c r="I384" s="145"/>
+      <c r="I384" s="121"/>
       <c r="J384" s="54"/>
       <c r="K384" s="54"/>
       <c r="L384" s="54"/>
@@ -24515,7 +26067,7 @@
       <c r="F385" s="54"/>
       <c r="G385" s="54"/>
       <c r="H385" s="54"/>
-      <c r="I385" s="145"/>
+      <c r="I385" s="121"/>
       <c r="J385" s="54"/>
       <c r="K385" s="54"/>
       <c r="L385" s="54"/>
@@ -24531,7 +26083,7 @@
       <c r="F386" s="54"/>
       <c r="G386" s="54"/>
       <c r="H386" s="54"/>
-      <c r="I386" s="145"/>
+      <c r="I386" s="121"/>
       <c r="J386" s="54"/>
       <c r="K386" s="54"/>
       <c r="L386" s="54"/>
@@ -24547,7 +26099,7 @@
       <c r="F387" s="54"/>
       <c r="G387" s="54"/>
       <c r="H387" s="54"/>
-      <c r="I387" s="145"/>
+      <c r="I387" s="121"/>
       <c r="J387" s="54"/>
       <c r="K387" s="54"/>
       <c r="L387" s="54"/>
@@ -24563,7 +26115,7 @@
       <c r="F388" s="54"/>
       <c r="G388" s="54"/>
       <c r="H388" s="54"/>
-      <c r="I388" s="145"/>
+      <c r="I388" s="121"/>
       <c r="J388" s="54"/>
       <c r="K388" s="54"/>
       <c r="L388" s="54"/>
@@ -24579,7 +26131,7 @@
       <c r="F389" s="54"/>
       <c r="G389" s="54"/>
       <c r="H389" s="54"/>
-      <c r="I389" s="145"/>
+      <c r="I389" s="121"/>
       <c r="J389" s="54"/>
       <c r="K389" s="54"/>
       <c r="L389" s="54"/>
@@ -24595,7 +26147,7 @@
       <c r="F390" s="54"/>
       <c r="G390" s="54"/>
       <c r="H390" s="54"/>
-      <c r="I390" s="145"/>
+      <c r="I390" s="121"/>
       <c r="J390" s="54"/>
       <c r="K390" s="54"/>
       <c r="L390" s="54"/>
@@ -24611,7 +26163,7 @@
       <c r="F391" s="54"/>
       <c r="G391" s="54"/>
       <c r="H391" s="54"/>
-      <c r="I391" s="145"/>
+      <c r="I391" s="121"/>
       <c r="J391" s="54"/>
       <c r="K391" s="54"/>
       <c r="L391" s="54"/>
@@ -24627,7 +26179,7 @@
       <c r="F392" s="54"/>
       <c r="G392" s="54"/>
       <c r="H392" s="54"/>
-      <c r="I392" s="145"/>
+      <c r="I392" s="121"/>
       <c r="J392" s="54"/>
       <c r="K392" s="54"/>
       <c r="L392" s="54"/>
@@ -24643,7 +26195,7 @@
       <c r="F393" s="54"/>
       <c r="G393" s="54"/>
       <c r="H393" s="54"/>
-      <c r="I393" s="145"/>
+      <c r="I393" s="121"/>
       <c r="J393" s="54"/>
       <c r="K393" s="54"/>
       <c r="L393" s="54"/>
@@ -24659,7 +26211,7 @@
       <c r="F394" s="54"/>
       <c r="G394" s="54"/>
       <c r="H394" s="54"/>
-      <c r="I394" s="145"/>
+      <c r="I394" s="121"/>
       <c r="J394" s="54"/>
       <c r="K394" s="54"/>
       <c r="L394" s="54"/>
@@ -24675,7 +26227,7 @@
       <c r="F395" s="54"/>
       <c r="G395" s="54"/>
       <c r="H395" s="54"/>
-      <c r="I395" s="145"/>
+      <c r="I395" s="121"/>
       <c r="J395" s="54"/>
       <c r="K395" s="54"/>
       <c r="L395" s="54"/>
@@ -24691,7 +26243,7 @@
       <c r="F396" s="54"/>
       <c r="G396" s="54"/>
       <c r="H396" s="54"/>
-      <c r="I396" s="145"/>
+      <c r="I396" s="121"/>
       <c r="J396" s="54"/>
       <c r="K396" s="54"/>
       <c r="L396" s="54"/>
@@ -24707,7 +26259,7 @@
       <c r="F397" s="54"/>
       <c r="G397" s="54"/>
       <c r="H397" s="54"/>
-      <c r="I397" s="145"/>
+      <c r="I397" s="121"/>
       <c r="J397" s="54"/>
       <c r="K397" s="54"/>
       <c r="L397" s="54"/>
@@ -24723,7 +26275,7 @@
       <c r="F398" s="54"/>
       <c r="G398" s="54"/>
       <c r="H398" s="54"/>
-      <c r="I398" s="145"/>
+      <c r="I398" s="121"/>
       <c r="J398" s="54"/>
       <c r="K398" s="54"/>
       <c r="L398" s="54"/>
@@ -24739,7 +26291,7 @@
       <c r="F399" s="54"/>
       <c r="G399" s="54"/>
       <c r="H399" s="54"/>
-      <c r="I399" s="145"/>
+      <c r="I399" s="121"/>
       <c r="J399" s="54"/>
       <c r="K399" s="54"/>
       <c r="L399" s="54"/>
@@ -24755,7 +26307,7 @@
       <c r="F400" s="54"/>
       <c r="G400" s="54"/>
       <c r="H400" s="54"/>
-      <c r="I400" s="145"/>
+      <c r="I400" s="121"/>
       <c r="J400" s="54"/>
       <c r="K400" s="54"/>
       <c r="L400" s="54"/>
@@ -24771,7 +26323,7 @@
       <c r="F401" s="54"/>
       <c r="G401" s="54"/>
       <c r="H401" s="54"/>
-      <c r="I401" s="145"/>
+      <c r="I401" s="121"/>
       <c r="J401" s="54"/>
       <c r="K401" s="54"/>
       <c r="L401" s="54"/>
@@ -24787,7 +26339,7 @@
       <c r="F402" s="54"/>
       <c r="G402" s="54"/>
       <c r="H402" s="54"/>
-      <c r="I402" s="145"/>
+      <c r="I402" s="121"/>
       <c r="J402" s="54"/>
       <c r="K402" s="54"/>
       <c r="L402" s="54"/>
@@ -24803,7 +26355,7 @@
       <c r="F403" s="54"/>
       <c r="G403" s="54"/>
       <c r="H403" s="54"/>
-      <c r="I403" s="145"/>
+      <c r="I403" s="121"/>
       <c r="J403" s="54"/>
       <c r="K403" s="54"/>
       <c r="L403" s="54"/>
@@ -24819,7 +26371,7 @@
       <c r="F404" s="54"/>
       <c r="G404" s="54"/>
       <c r="H404" s="54"/>
-      <c r="I404" s="145"/>
+      <c r="I404" s="121"/>
       <c r="J404" s="54"/>
       <c r="K404" s="54"/>
       <c r="L404" s="54"/>
@@ -24835,7 +26387,7 @@
       <c r="F405" s="54"/>
       <c r="G405" s="54"/>
       <c r="H405" s="54"/>
-      <c r="I405" s="145"/>
+      <c r="I405" s="121"/>
       <c r="J405" s="54"/>
       <c r="K405" s="54"/>
       <c r="L405" s="54"/>
@@ -24851,7 +26403,7 @@
       <c r="F406" s="54"/>
       <c r="G406" s="54"/>
       <c r="H406" s="54"/>
-      <c r="I406" s="145"/>
+      <c r="I406" s="121"/>
       <c r="J406" s="54"/>
       <c r="K406" s="54"/>
       <c r="L406" s="54"/>
@@ -24867,7 +26419,7 @@
       <c r="F407" s="54"/>
       <c r="G407" s="54"/>
       <c r="H407" s="54"/>
-      <c r="I407" s="145"/>
+      <c r="I407" s="121"/>
       <c r="J407" s="54"/>
       <c r="K407" s="54"/>
       <c r="L407" s="54"/>
@@ -24883,7 +26435,7 @@
       <c r="F408" s="54"/>
       <c r="G408" s="54"/>
       <c r="H408" s="54"/>
-      <c r="I408" s="145"/>
+      <c r="I408" s="121"/>
       <c r="J408" s="54"/>
       <c r="K408" s="54"/>
       <c r="L408" s="54"/>
@@ -24899,7 +26451,7 @@
       <c r="F409" s="54"/>
       <c r="G409" s="54"/>
       <c r="H409" s="54"/>
-      <c r="I409" s="145"/>
+      <c r="I409" s="121"/>
       <c r="J409" s="54"/>
       <c r="K409" s="54"/>
       <c r="L409" s="54"/>
@@ -24915,7 +26467,7 @@
       <c r="F410" s="54"/>
       <c r="G410" s="54"/>
       <c r="H410" s="54"/>
-      <c r="I410" s="145"/>
+      <c r="I410" s="121"/>
       <c r="J410" s="54"/>
       <c r="K410" s="54"/>
       <c r="L410" s="54"/>
@@ -24931,7 +26483,7 @@
       <c r="F411" s="54"/>
       <c r="G411" s="54"/>
       <c r="H411" s="54"/>
-      <c r="I411" s="145"/>
+      <c r="I411" s="121"/>
       <c r="J411" s="54"/>
       <c r="K411" s="54"/>
       <c r="L411" s="54"/>
@@ -24947,7 +26499,7 @@
       <c r="F412" s="54"/>
       <c r="G412" s="54"/>
       <c r="H412" s="54"/>
-      <c r="I412" s="145"/>
+      <c r="I412" s="121"/>
       <c r="J412" s="54"/>
       <c r="K412" s="54"/>
       <c r="L412" s="54"/>
@@ -24963,7 +26515,7 @@
       <c r="F413" s="54"/>
       <c r="G413" s="54"/>
       <c r="H413" s="54"/>
-      <c r="I413" s="145"/>
+      <c r="I413" s="121"/>
       <c r="J413" s="54"/>
       <c r="K413" s="54"/>
       <c r="L413" s="54"/>
@@ -24979,7 +26531,7 @@
       <c r="F414" s="54"/>
       <c r="G414" s="54"/>
       <c r="H414" s="54"/>
-      <c r="I414" s="145"/>
+      <c r="I414" s="121"/>
       <c r="J414" s="54"/>
       <c r="K414" s="54"/>
       <c r="L414" s="54"/>
@@ -24995,7 +26547,7 @@
       <c r="F415" s="54"/>
       <c r="G415" s="54"/>
       <c r="H415" s="54"/>
-      <c r="I415" s="145"/>
+      <c r="I415" s="121"/>
       <c r="J415" s="54"/>
       <c r="K415" s="54"/>
       <c r="L415" s="54"/>
@@ -25011,7 +26563,7 @@
       <c r="F416" s="54"/>
       <c r="G416" s="54"/>
       <c r="H416" s="54"/>
-      <c r="I416" s="145"/>
+      <c r="I416" s="121"/>
       <c r="J416" s="54"/>
       <c r="K416" s="54"/>
       <c r="L416" s="54"/>
@@ -25027,7 +26579,7 @@
       <c r="F417" s="54"/>
       <c r="G417" s="54"/>
       <c r="H417" s="54"/>
-      <c r="I417" s="145"/>
+      <c r="I417" s="121"/>
       <c r="J417" s="54"/>
       <c r="K417" s="54"/>
       <c r="L417" s="54"/>
@@ -25043,7 +26595,7 @@
       <c r="F418" s="54"/>
       <c r="G418" s="54"/>
       <c r="H418" s="54"/>
-      <c r="I418" s="145"/>
+      <c r="I418" s="121"/>
       <c r="J418" s="54"/>
       <c r="K418" s="54"/>
       <c r="L418" s="54"/>
@@ -25059,7 +26611,7 @@
       <c r="F419" s="54"/>
       <c r="G419" s="54"/>
       <c r="H419" s="54"/>
-      <c r="I419" s="145"/>
+      <c r="I419" s="121"/>
       <c r="J419" s="54"/>
       <c r="K419" s="54"/>
       <c r="L419" s="54"/>
@@ -25075,7 +26627,7 @@
       <c r="F420" s="54"/>
       <c r="G420" s="54"/>
       <c r="H420" s="54"/>
-      <c r="I420" s="145"/>
+      <c r="I420" s="121"/>
       <c r="J420" s="54"/>
       <c r="K420" s="54"/>
       <c r="L420" s="54"/>
@@ -25091,7 +26643,7 @@
       <c r="F421" s="54"/>
       <c r="G421" s="54"/>
       <c r="H421" s="54"/>
-      <c r="I421" s="145"/>
+      <c r="I421" s="121"/>
       <c r="J421" s="54"/>
       <c r="K421" s="54"/>
       <c r="L421" s="54"/>
@@ -25107,7 +26659,7 @@
       <c r="F422" s="54"/>
       <c r="G422" s="54"/>
       <c r="H422" s="54"/>
-      <c r="I422" s="145"/>
+      <c r="I422" s="121"/>
       <c r="J422" s="54"/>
       <c r="K422" s="54"/>
       <c r="L422" s="54"/>
@@ -25123,7 +26675,7 @@
       <c r="F423" s="54"/>
       <c r="G423" s="54"/>
       <c r="H423" s="54"/>
-      <c r="I423" s="145"/>
+      <c r="I423" s="121"/>
       <c r="J423" s="54"/>
       <c r="K423" s="54"/>
       <c r="L423" s="54"/>
@@ -25139,7 +26691,7 @@
       <c r="F424" s="54"/>
       <c r="G424" s="54"/>
       <c r="H424" s="54"/>
-      <c r="I424" s="145"/>
+      <c r="I424" s="121"/>
       <c r="J424" s="54"/>
       <c r="K424" s="54"/>
       <c r="L424" s="54"/>
@@ -25155,7 +26707,7 @@
       <c r="F425" s="54"/>
       <c r="G425" s="54"/>
       <c r="H425" s="54"/>
-      <c r="I425" s="145"/>
+      <c r="I425" s="121"/>
       <c r="J425" s="54"/>
       <c r="K425" s="54"/>
       <c r="L425" s="54"/>
@@ -25171,7 +26723,7 @@
       <c r="F426" s="54"/>
       <c r="G426" s="54"/>
       <c r="H426" s="54"/>
-      <c r="I426" s="145"/>
+      <c r="I426" s="121"/>
       <c r="J426" s="54"/>
       <c r="K426" s="54"/>
       <c r="L426" s="54"/>
@@ -25187,7 +26739,7 @@
       <c r="F427" s="54"/>
       <c r="G427" s="54"/>
       <c r="H427" s="54"/>
-      <c r="I427" s="145"/>
+      <c r="I427" s="121"/>
       <c r="J427" s="54"/>
       <c r="K427" s="54"/>
       <c r="L427" s="54"/>
@@ -25203,7 +26755,7 @@
       <c r="F428" s="54"/>
       <c r="G428" s="54"/>
       <c r="H428" s="54"/>
-      <c r="I428" s="145"/>
+      <c r="I428" s="121"/>
       <c r="J428" s="54"/>
       <c r="K428" s="54"/>
       <c r="L428" s="54"/>
@@ -25219,7 +26771,7 @@
       <c r="F429" s="54"/>
       <c r="G429" s="54"/>
       <c r="H429" s="54"/>
-      <c r="I429" s="145"/>
+      <c r="I429" s="121"/>
       <c r="J429" s="54"/>
       <c r="K429" s="54"/>
       <c r="L429" s="54"/>
@@ -25235,7 +26787,7 @@
       <c r="F430" s="54"/>
       <c r="G430" s="54"/>
       <c r="H430" s="54"/>
-      <c r="I430" s="145"/>
+      <c r="I430" s="121"/>
       <c r="J430" s="54"/>
       <c r="K430" s="54"/>
       <c r="L430" s="54"/>
@@ -25251,7 +26803,7 @@
       <c r="F431" s="54"/>
       <c r="G431" s="54"/>
       <c r="H431" s="54"/>
-      <c r="I431" s="145"/>
+      <c r="I431" s="121"/>
       <c r="J431" s="54"/>
       <c r="K431" s="54"/>
       <c r="L431" s="54"/>
@@ -25267,7 +26819,7 @@
       <c r="F432" s="54"/>
       <c r="G432" s="54"/>
       <c r="H432" s="54"/>
-      <c r="I432" s="145"/>
+      <c r="I432" s="121"/>
       <c r="J432" s="54"/>
       <c r="K432" s="54"/>
       <c r="L432" s="54"/>
@@ -25283,7 +26835,7 @@
       <c r="F433" s="54"/>
       <c r="G433" s="54"/>
       <c r="H433" s="54"/>
-      <c r="I433" s="145"/>
+      <c r="I433" s="121"/>
       <c r="J433" s="54"/>
       <c r="K433" s="54"/>
       <c r="L433" s="54"/>
@@ -25299,7 +26851,7 @@
       <c r="F434" s="54"/>
       <c r="G434" s="54"/>
       <c r="H434" s="54"/>
-      <c r="I434" s="145"/>
+      <c r="I434" s="121"/>
       <c r="J434" s="54"/>
       <c r="K434" s="54"/>
       <c r="L434" s="54"/>
@@ -25315,7 +26867,7 @@
       <c r="F435" s="54"/>
       <c r="G435" s="54"/>
       <c r="H435" s="54"/>
-      <c r="I435" s="145"/>
+      <c r="I435" s="121"/>
       <c r="J435" s="54"/>
       <c r="K435" s="54"/>
       <c r="L435" s="54"/>
@@ -25331,7 +26883,7 @@
       <c r="F436" s="54"/>
       <c r="G436" s="54"/>
       <c r="H436" s="54"/>
-      <c r="I436" s="145"/>
+      <c r="I436" s="121"/>
       <c r="J436" s="54"/>
       <c r="K436" s="54"/>
       <c r="L436" s="54"/>
@@ -25347,7 +26899,7 @@
       <c r="F437" s="54"/>
       <c r="G437" s="54"/>
       <c r="H437" s="54"/>
-      <c r="I437" s="145"/>
+      <c r="I437" s="121"/>
       <c r="J437" s="54"/>
       <c r="K437" s="54"/>
       <c r="L437" s="54"/>
@@ -25363,7 +26915,7 @@
       <c r="F438" s="54"/>
       <c r="G438" s="54"/>
       <c r="H438" s="54"/>
-      <c r="I438" s="145"/>
+      <c r="I438" s="121"/>
       <c r="J438" s="54"/>
       <c r="K438" s="54"/>
       <c r="L438" s="54"/>
@@ -25379,7 +26931,7 @@
       <c r="F439" s="54"/>
       <c r="G439" s="54"/>
       <c r="H439" s="54"/>
-      <c r="I439" s="145"/>
+      <c r="I439" s="121"/>
       <c r="J439" s="54"/>
       <c r="K439" s="54"/>
       <c r="L439" s="54"/>
@@ -25395,7 +26947,7 @@
       <c r="F440" s="54"/>
       <c r="G440" s="54"/>
       <c r="H440" s="54"/>
-      <c r="I440" s="145"/>
+      <c r="I440" s="121"/>
       <c r="J440" s="54"/>
       <c r="K440" s="54"/>
       <c r="L440" s="54"/>
@@ -25411,7 +26963,7 @@
       <c r="F441" s="54"/>
       <c r="G441" s="54"/>
       <c r="H441" s="54"/>
-      <c r="I441" s="145"/>
+      <c r="I441" s="121"/>
       <c r="J441" s="54"/>
       <c r="K441" s="54"/>
       <c r="L441" s="54"/>
@@ -25427,7 +26979,7 @@
       <c r="F442" s="54"/>
       <c r="G442" s="54"/>
       <c r="H442" s="54"/>
-      <c r="I442" s="145"/>
+      <c r="I442" s="121"/>
       <c r="J442" s="54"/>
       <c r="K442" s="54"/>
       <c r="L442" s="54"/>
@@ -25443,7 +26995,7 @@
       <c r="F443" s="54"/>
       <c r="G443" s="54"/>
       <c r="H443" s="54"/>
-      <c r="I443" s="145"/>
+      <c r="I443" s="121"/>
       <c r="J443" s="54"/>
       <c r="K443" s="54"/>
       <c r="L443" s="54"/>
@@ -25459,7 +27011,7 @@
       <c r="F444" s="54"/>
       <c r="G444" s="54"/>
       <c r="H444" s="54"/>
-      <c r="I444" s="145"/>
+      <c r="I444" s="121"/>
       <c r="J444" s="54"/>
       <c r="K444" s="54"/>
       <c r="L444" s="54"/>
@@ -25475,7 +27027,7 @@
       <c r="F445" s="54"/>
       <c r="G445" s="54"/>
       <c r="H445" s="54"/>
-      <c r="I445" s="145"/>
+      <c r="I445" s="121"/>
       <c r="J445" s="54"/>
       <c r="K445" s="54"/>
       <c r="L445" s="54"/>
@@ -25491,7 +27043,7 @@
       <c r="F446" s="54"/>
       <c r="G446" s="54"/>
       <c r="H446" s="54"/>
-      <c r="I446" s="145"/>
+      <c r="I446" s="121"/>
       <c r="J446" s="54"/>
       <c r="K446" s="54"/>
       <c r="L446" s="54"/>
@@ -25507,7 +27059,7 @@
       <c r="F447" s="54"/>
       <c r="G447" s="54"/>
       <c r="H447" s="54"/>
-      <c r="I447" s="145"/>
+      <c r="I447" s="121"/>
       <c r="J447" s="54"/>
       <c r="K447" s="54"/>
       <c r="L447" s="54"/>
@@ -25523,7 +27075,7 @@
       <c r="F448" s="54"/>
       <c r="G448" s="54"/>
       <c r="H448" s="54"/>
-      <c r="I448" s="145"/>
+      <c r="I448" s="121"/>
       <c r="J448" s="54"/>
       <c r="K448" s="54"/>
       <c r="L448" s="54"/>
@@ -25539,7 +27091,7 @@
       <c r="F449" s="54"/>
       <c r="G449" s="54"/>
       <c r="H449" s="54"/>
-      <c r="I449" s="145"/>
+      <c r="I449" s="121"/>
       <c r="J449" s="54"/>
       <c r="K449" s="54"/>
       <c r="L449" s="54"/>
@@ -25555,7 +27107,7 @@
       <c r="F450" s="54"/>
       <c r="G450" s="54"/>
       <c r="H450" s="54"/>
-      <c r="I450" s="145"/>
+      <c r="I450" s="121"/>
       <c r="J450" s="54"/>
       <c r="K450" s="54"/>
       <c r="L450" s="54"/>
@@ -25571,7 +27123,7 @@
       <c r="F451" s="54"/>
       <c r="G451" s="54"/>
       <c r="H451" s="54"/>
-      <c r="I451" s="145"/>
+      <c r="I451" s="121"/>
       <c r="J451" s="54"/>
       <c r="K451" s="54"/>
       <c r="L451" s="54"/>
@@ -25587,7 +27139,7 @@
       <c r="F452" s="54"/>
       <c r="G452" s="54"/>
       <c r="H452" s="54"/>
-      <c r="I452" s="145"/>
+      <c r="I452" s="121"/>
       <c r="J452" s="54"/>
       <c r="K452" s="54"/>
       <c r="L452" s="54"/>
@@ -25603,7 +27155,7 @@
       <c r="F453" s="54"/>
       <c r="G453" s="54"/>
       <c r="H453" s="54"/>
-      <c r="I453" s="145"/>
+      <c r="I453" s="121"/>
       <c r="J453" s="54"/>
       <c r="K453" s="54"/>
       <c r="L453" s="54"/>
@@ -25619,7 +27171,7 @@
       <c r="F454" s="54"/>
       <c r="G454" s="54"/>
       <c r="H454" s="54"/>
-      <c r="I454" s="145"/>
+      <c r="I454" s="121"/>
       <c r="J454" s="54"/>
       <c r="K454" s="54"/>
       <c r="L454" s="54"/>
@@ -25635,7 +27187,7 @@
       <c r="F455" s="54"/>
       <c r="G455" s="54"/>
       <c r="H455" s="54"/>
-      <c r="I455" s="145"/>
+      <c r="I455" s="121"/>
       <c r="J455" s="54"/>
       <c r="K455" s="54"/>
       <c r="L455" s="54"/>
@@ -25651,7 +27203,7 @@
       <c r="F456" s="54"/>
       <c r="G456" s="54"/>
       <c r="H456" s="54"/>
-      <c r="I456" s="145"/>
+      <c r="I456" s="121"/>
       <c r="J456" s="54"/>
       <c r="K456" s="54"/>
       <c r="L456" s="54"/>
@@ -25666,7 +27218,7 @@
       <c r="F457" s="54"/>
       <c r="G457" s="54"/>
       <c r="H457" s="54"/>
-      <c r="I457" s="145"/>
+      <c r="I457" s="121"/>
       <c r="J457" s="54"/>
       <c r="K457" s="54"/>
       <c r="L457" s="54"/>
@@ -25681,7 +27233,7 @@
       <c r="F458" s="54"/>
       <c r="G458" s="54"/>
       <c r="H458" s="54"/>
-      <c r="I458" s="145"/>
+      <c r="I458" s="121"/>
       <c r="J458" s="54"/>
       <c r="K458" s="54"/>
       <c r="L458" s="54"/>
@@ -25696,7 +27248,7 @@
       <c r="F459" s="54"/>
       <c r="G459" s="54"/>
       <c r="H459" s="54"/>
-      <c r="I459" s="145"/>
+      <c r="I459" s="121"/>
       <c r="J459" s="54"/>
       <c r="K459" s="54"/>
       <c r="L459" s="54"/>
@@ -25721,10 +27273,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0E6BBF3-D5C5-4DEF-86E8-89300EE052BA}">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="24.46484375" customWidth="1"/>
+    <col min="3" max="3" width="27.53125" customWidth="1"/>
+    <col min="4" max="4" width="28.53125" customWidth="1"/>
+    <col min="10" max="10" width="30.265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>116</v>
       </c>
@@ -25734,8 +27292,41 @@
       <c r="C1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1942</v>
       </c>
@@ -25746,7 +27337,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1943</v>
       </c>
@@ -25757,7 +27348,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1944</v>
       </c>
@@ -25768,7 +27359,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1945</v>
       </c>
@@ -25779,7 +27370,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1946</v>
       </c>
@@ -25790,7 +27381,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1947</v>
       </c>
@@ -25801,7 +27392,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1948</v>
       </c>
@@ -25812,7 +27403,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1949</v>
       </c>
@@ -25823,7 +27414,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1950</v>
       </c>
@@ -25834,7 +27425,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1951</v>
       </c>
@@ -25845,7 +27436,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1952</v>
       </c>
@@ -25856,7 +27447,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1953</v>
       </c>
@@ -25867,7 +27458,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1954</v>
       </c>
@@ -25878,7 +27469,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1955</v>
       </c>
@@ -25889,7 +27480,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1956</v>
       </c>
@@ -25900,7 +27491,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1957</v>
       </c>
@@ -25911,7 +27502,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1958</v>
       </c>
@@ -25922,7 +27513,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1959</v>
       </c>
@@ -25933,7 +27524,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1960</v>
       </c>
@@ -25943,8 +27534,17 @@
       <c r="C20">
         <v>272</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>31.118707178382301</v>
+      </c>
+      <c r="E20">
+        <v>2002.3020946858301</v>
+      </c>
+      <c r="F20">
+        <v>4.4438589788337799</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1961</v>
       </c>
@@ -25954,8 +27554,17 @@
       <c r="C21">
         <v>289</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <v>32.132255556799201</v>
+      </c>
+      <c r="E21">
+        <v>2125.3559115489302</v>
+      </c>
+      <c r="F21">
+        <v>4.1929793613585602</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1962</v>
       </c>
@@ -25965,8 +27574,17 @@
       <c r="C22">
         <v>310</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22">
+        <v>33.920921480087301</v>
+      </c>
+      <c r="E22">
+        <v>2306.35129327409</v>
+      </c>
+      <c r="F22">
+        <v>4.10305136108955</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1963</v>
       </c>
@@ -25976,8 +27594,17 @@
       <c r="C23">
         <v>332</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23">
+        <v>35.799562336980003</v>
+      </c>
+      <c r="E23">
+        <v>2486.9239964253202</v>
+      </c>
+      <c r="F23">
+        <v>4.0234194952550997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1964</v>
       </c>
@@ -25987,8 +27614,17 @@
       <c r="C24">
         <v>358</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <v>38.931493113336501</v>
+      </c>
+      <c r="E24">
+        <v>2750.2763994985398</v>
+      </c>
+      <c r="F24">
+        <v>4.0141228756525802</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1965</v>
       </c>
@@ -25998,8 +27634,17 @@
       <c r="C25">
         <v>384</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25">
+        <v>42.586521555032398</v>
+      </c>
+      <c r="E25">
+        <v>3037.1003712186898</v>
+      </c>
+      <c r="F25">
+        <v>4.1388621472084601</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1966</v>
       </c>
@@ -26009,8 +27654,17 @@
       <c r="C26">
         <v>412</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <v>49.261579910475398</v>
+      </c>
+      <c r="E26">
+        <v>3544.4691977185198</v>
+      </c>
+      <c r="F26">
+        <v>4.4980694056547001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1967</v>
       </c>
@@ -26020,8 +27674,17 @@
       <c r="C27">
         <v>439</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27">
+        <v>55.083927608601897</v>
+      </c>
+      <c r="E27">
+        <v>4007.68623709144</v>
+      </c>
+      <c r="F27">
+        <v>4.7247994182413802</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1968</v>
       </c>
@@ -26031,8 +27694,17 @@
       <c r="C28">
         <v>460</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28">
+        <v>59.568011610878798</v>
+      </c>
+      <c r="E28">
+        <v>4383.2525663749102</v>
+      </c>
+      <c r="F28">
+        <v>4.8394352248711403</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1969</v>
       </c>
@@ -26042,8 +27714,17 @@
       <c r="C29">
         <v>488</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D29">
+        <v>65.220008601375397</v>
+      </c>
+      <c r="E29">
+        <v>4861.7603211809301</v>
+      </c>
+      <c r="F29">
+        <v>4.9539267659958304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1970</v>
       </c>
@@ -26053,8 +27734,17 @@
       <c r="C30">
         <v>534</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30">
+        <v>72.712181977453895</v>
+      </c>
+      <c r="E30">
+        <v>5468.2469334324396</v>
+      </c>
+      <c r="F30">
+        <v>5.0022134193630796</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1971</v>
       </c>
@@ -26064,8 +27754,17 @@
       <c r="C31">
         <v>601</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D31">
+        <v>85.024103094571899</v>
+      </c>
+      <c r="E31">
+        <v>6471.6946311464399</v>
+      </c>
+      <c r="F31">
+        <v>5.21141477125152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1972</v>
       </c>
@@ -26075,8 +27774,17 @@
       <c r="C32">
         <v>667</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32">
+        <v>94.653939975134094</v>
+      </c>
+      <c r="E32">
+        <v>7270.5584373700003</v>
+      </c>
+      <c r="F32">
+        <v>5.1667026151018502</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1973</v>
       </c>
@@ -26086,8 +27794,17 @@
       <c r="C33">
         <v>747</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33">
+        <v>106.14335772587</v>
+      </c>
+      <c r="E33">
+        <v>8204.0324053479799</v>
+      </c>
+      <c r="F33">
+        <v>5.2316343453217504</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1974</v>
       </c>
@@ -26097,8 +27814,17 @@
       <c r="C34">
         <v>838</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D34">
+        <v>122.067853787031</v>
+      </c>
+      <c r="E34">
+        <v>9462.7000255706698</v>
+      </c>
+      <c r="F34">
+        <v>5.5621388209935798</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1975</v>
       </c>
@@ -26108,8 +27834,17 @@
       <c r="C35">
         <v>901</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35">
+        <v>139.20490842117999</v>
+      </c>
+      <c r="E35">
+        <v>10697.6188023508</v>
+      </c>
+      <c r="F35">
+        <v>6.3304165375367498</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1976</v>
       </c>
@@ -26119,8 +27854,17 @@
       <c r="C36">
         <v>920</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36">
+        <v>147.51747509218399</v>
+      </c>
+      <c r="E36">
+        <v>11210.738037105601</v>
+      </c>
+      <c r="F36">
+        <v>6.5497086019469499</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1977</v>
       </c>
@@ -26130,8 +27874,17 @@
       <c r="C37">
         <v>942</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37">
+        <v>152.08863672088</v>
+      </c>
+      <c r="E37">
+        <v>11527.1019543489</v>
+      </c>
+      <c r="F37">
+        <v>6.5576187404382997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1978</v>
       </c>
@@ -26141,8 +27894,17 @@
       <c r="C38">
         <v>972</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38">
+        <v>157.99913292437699</v>
+      </c>
+      <c r="E38">
+        <v>12007.302105720901</v>
+      </c>
+      <c r="F38">
+        <v>6.5657629487225604</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1979</v>
       </c>
@@ -26152,8 +27914,17 @@
       <c r="C39">
         <v>1004</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39">
+        <v>167.51766182124001</v>
+      </c>
+      <c r="E39">
+        <v>12766.856042720399</v>
+      </c>
+      <c r="F39">
+        <v>6.6785960428148696</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1980</v>
       </c>
@@ -26163,8 +27934,17 @@
       <c r="C40">
         <v>1058</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D40">
+        <v>179.01253728536</v>
+      </c>
+      <c r="E40">
+        <v>13715.940606804301</v>
+      </c>
+      <c r="F40">
+        <v>6.6786427674933604</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1981</v>
       </c>
@@ -26174,8 +27954,17 @@
       <c r="C41">
         <v>1124</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D41">
+        <v>194.77620972478601</v>
+      </c>
+      <c r="E41">
+        <v>14851.468231712401</v>
+      </c>
+      <c r="F41">
+        <v>6.7362381542960703</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1982</v>
       </c>
@@ -26185,8 +27974,17 @@
       <c r="C42">
         <v>1203</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42">
+        <v>209.33571987250599</v>
+      </c>
+      <c r="E42">
+        <v>16055.149989297201</v>
+      </c>
+      <c r="F42">
+        <v>6.8737316536709496</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1983</v>
       </c>
@@ -26196,8 +27994,17 @@
       <c r="C43">
         <v>1248</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43">
+        <v>225.974808360879</v>
+      </c>
+      <c r="E43">
+        <v>17405.7719830438</v>
+      </c>
+      <c r="F43">
+        <v>7.23344787714466</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1984</v>
       </c>
@@ -26207,8 +28014,17 @@
       <c r="C44">
         <v>1283</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44">
+        <v>233.01724988762601</v>
+      </c>
+      <c r="E44">
+        <v>18012.786599264698</v>
+      </c>
+      <c r="F44">
+        <v>7.00376625441959</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1985</v>
       </c>
@@ -26218,8 +28034,17 @@
       <c r="C45">
         <v>1323</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45">
+        <v>244.50645425445799</v>
+      </c>
+      <c r="E45">
+        <v>18984.552046585799</v>
+      </c>
+      <c r="F45">
+        <v>6.9619607879434602</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1986</v>
       </c>
@@ -26229,8 +28054,17 @@
       <c r="C46">
         <v>1370</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46">
+        <v>260.78656057574699</v>
+      </c>
+      <c r="E46">
+        <v>20354.262224376202</v>
+      </c>
+      <c r="F46">
+        <v>7.1122281151148803</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1987</v>
       </c>
@@ -26240,8 +28074,17 @@
       <c r="C47">
         <v>1403</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47">
+        <v>275.19612860530799</v>
+      </c>
+      <c r="E47">
+        <v>21614.253990136502</v>
+      </c>
+      <c r="F47">
+        <v>7.2750458539937801</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1988</v>
       </c>
@@ -26251,8 +28094,17 @@
       <c r="C48">
         <v>1452</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D48">
+        <v>291.75161229077798</v>
+      </c>
+      <c r="E48">
+        <v>23083.571951465299</v>
+      </c>
+      <c r="F48">
+        <v>7.3188104915637702</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1989</v>
       </c>
@@ -26262,8 +28114,17 @@
       <c r="C49">
         <v>1507</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49">
+        <v>312.90841773603302</v>
+      </c>
+      <c r="E49">
+        <v>24958.494723557302</v>
+      </c>
+      <c r="F49">
+        <v>7.3312386062915502</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1990</v>
       </c>
@@ -26273,8 +28134,17 @@
       <c r="C50">
         <v>1595</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D50">
+        <v>333.51101523092802</v>
+      </c>
+      <c r="E50">
+        <v>26863.397789647501</v>
+      </c>
+      <c r="F50">
+        <v>7.2761344120397498</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1991</v>
       </c>
@@ -26284,8 +28154,17 @@
       <c r="C51">
         <v>1706</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51">
+        <v>371.26240520059702</v>
+      </c>
+      <c r="E51">
+        <v>30294.914251093702</v>
+      </c>
+      <c r="F51">
+        <v>7.8564624268402996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1992</v>
       </c>
@@ -26295,8 +28174,17 @@
       <c r="C52">
         <v>1788</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D52">
+        <v>391.223048807748</v>
+      </c>
+      <c r="E52">
+        <v>32277.6080415781</v>
+      </c>
+      <c r="F52">
+        <v>8.2000803498254093</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1993</v>
       </c>
@@ -26306,8 +28194,17 @@
       <c r="C53">
         <v>1836</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53">
+        <v>400.98170698541998</v>
+      </c>
+      <c r="E53">
+        <v>33385.4057127161</v>
+      </c>
+      <c r="F53">
+        <v>8.2994972424103892</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1994</v>
       </c>
@@ -26317,8 +28214,17 @@
       <c r="C54">
         <v>1862</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D54">
+        <v>413.07856296491298</v>
+      </c>
+      <c r="E54">
+        <v>34667.838980783003</v>
+      </c>
+      <c r="F54">
+        <v>8.4106318056980296</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>1995</v>
       </c>
@@ -26328,8 +28234,17 @@
       <c r="C55">
         <v>1887</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55">
+        <v>425.61578682178998</v>
+      </c>
+      <c r="E55">
+        <v>35959.527893556697</v>
+      </c>
+      <c r="F55">
+        <v>8.6186685755048593</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>1996</v>
       </c>
@@ -26339,8 +28254,17 @@
       <c r="C56">
         <v>1910</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D56">
+        <v>443.91078281492997</v>
+      </c>
+      <c r="E56">
+        <v>37671.2456333972</v>
+      </c>
+      <c r="F56">
+        <v>8.9614816949641298</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>1997</v>
       </c>
@@ -26350,8 +28274,17 @@
       <c r="C57">
         <v>1919</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D57">
+        <v>451.88980841428202</v>
+      </c>
+      <c r="E57">
+        <v>38440.849779143398</v>
+      </c>
+      <c r="F57">
+        <v>8.9851574232945808</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>1998</v>
       </c>
@@ -26361,8 +28294,17 @@
       <c r="C58">
         <v>1932</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D58">
+        <v>468.46652723537102</v>
+      </c>
+      <c r="E58">
+        <v>39969.5697253201</v>
+      </c>
+      <c r="F58">
+        <v>9.0849247640106103</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>1999</v>
       </c>
@@ -26372,8 +28314,41 @@
       <c r="C59">
         <v>1938</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D59">
+        <v>480.81456637682402</v>
+      </c>
+      <c r="E59">
+        <v>41219.2163334918</v>
+      </c>
+      <c r="F59">
+        <v>9.2117023327310292</v>
+      </c>
+      <c r="G59">
+        <v>100</v>
+      </c>
+      <c r="H59">
+        <v>100</v>
+      </c>
+      <c r="I59">
+        <v>100</v>
+      </c>
+      <c r="K59">
+        <f>B59/$B$59*100</f>
+        <v>100</v>
+      </c>
+      <c r="L59">
+        <f>C59/$C$59*100</f>
+        <v>100</v>
+      </c>
+      <c r="M59">
+        <v>494680.50768559601</v>
+      </c>
+      <c r="N59">
+        <f>M59/$M$59*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2000</v>
       </c>
@@ -26383,8 +28358,44 @@
       <c r="C60">
         <v>1963</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D60">
+        <v>498.27519242888502</v>
+      </c>
+      <c r="E60">
+        <v>42956.799624835498</v>
+      </c>
+      <c r="F60">
+        <v>9.1098944165392002</v>
+      </c>
+      <c r="G60">
+        <v>104.6</v>
+      </c>
+      <c r="H60">
+        <v>103.8</v>
+      </c>
+      <c r="I60">
+        <v>106.4</v>
+      </c>
+      <c r="J60" t="s">
+        <v>126</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ref="K60:K85" si="0">B60/$B$59*100</f>
+        <v>99.642857142857139</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ref="L60:L85" si="1">C60/$C$59*100</f>
+        <v>101.28998968008256</v>
+      </c>
+      <c r="M60">
+        <v>512653.323301428</v>
+      </c>
+      <c r="N60">
+        <f t="shared" ref="N60:N85" si="2">M60/$M$59*100</f>
+        <v>103.63321686150913</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2001</v>
       </c>
@@ -26394,8 +28405,44 @@
       <c r="C61">
         <v>2011</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D61">
+        <v>526.19068838696103</v>
+      </c>
+      <c r="E61">
+        <v>45631.122844482401</v>
+      </c>
+      <c r="F61">
+        <v>9.4349957837579801</v>
+      </c>
+      <c r="G61">
+        <v>110.3</v>
+      </c>
+      <c r="H61">
+        <v>109.8</v>
+      </c>
+      <c r="I61">
+        <v>111.1</v>
+      </c>
+      <c r="J61">
+        <v>-0.4</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="0"/>
+        <v>101.42857142857142</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="1"/>
+        <v>103.76676986584108</v>
+      </c>
+      <c r="M61">
+        <v>520815.77781889698</v>
+      </c>
+      <c r="N61">
+        <f t="shared" si="2"/>
+        <v>105.28326257599619</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2002</v>
       </c>
@@ -26405,8 +28452,44 @@
       <c r="C62">
         <v>2047</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D62">
+        <v>543.38755948914002</v>
+      </c>
+      <c r="E62">
+        <v>47501.329849814298</v>
+      </c>
+      <c r="F62">
+        <v>9.8534695572985296</v>
+      </c>
+      <c r="G62">
+        <v>119</v>
+      </c>
+      <c r="H62">
+        <v>120.8</v>
+      </c>
+      <c r="I62">
+        <v>115.4</v>
+      </c>
+      <c r="J62">
+        <v>-0.5</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="0"/>
+        <v>102.49999999999999</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="1"/>
+        <v>105.62435500515997</v>
+      </c>
+      <c r="M62">
+        <v>522797.01421946299</v>
+      </c>
+      <c r="N62">
+        <f t="shared" si="2"/>
+        <v>105.68377085756065</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2003</v>
       </c>
@@ -26416,8 +28499,44 @@
       <c r="C63">
         <v>2076</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D63">
+        <v>559.746747373978</v>
+      </c>
+      <c r="E63">
+        <v>49295.779906211901</v>
+      </c>
+      <c r="F63">
+        <v>10.1097458706484</v>
+      </c>
+      <c r="G63">
+        <v>127.4</v>
+      </c>
+      <c r="H63">
+        <v>133</v>
+      </c>
+      <c r="I63">
+        <v>116.4</v>
+      </c>
+      <c r="J63">
+        <v>-0.5</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="0"/>
+        <v>103.21428571428572</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="1"/>
+        <v>107.12074303405572</v>
+      </c>
+      <c r="M63">
+        <v>521311.10771313799</v>
+      </c>
+      <c r="N63">
+        <f t="shared" si="2"/>
+        <v>105.38339384992861</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2004</v>
       </c>
@@ -26427,8 +28546,44 @@
       <c r="C64">
         <v>2095</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D64">
+        <v>577.64079721063001</v>
+      </c>
+      <c r="E64">
+        <v>51222.586513051203</v>
+      </c>
+      <c r="F64">
+        <v>10.1983051102332</v>
+      </c>
+      <c r="G64">
+        <v>134</v>
+      </c>
+      <c r="H64">
+        <v>142.1</v>
+      </c>
+      <c r="I64">
+        <v>117.9</v>
+      </c>
+      <c r="J64">
+        <v>-0.4</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="0"/>
+        <v>103.21428571428572</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="1"/>
+        <v>108.10113519091846</v>
+      </c>
+      <c r="M64">
+        <v>534797.05567569402</v>
+      </c>
+      <c r="N64">
+        <f t="shared" si="2"/>
+        <v>108.10958737343152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2005</v>
       </c>
@@ -26438,8 +28593,44 @@
       <c r="C65">
         <v>2115</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D65">
+        <v>585.43600086755896</v>
+      </c>
+      <c r="E65">
+        <v>52247.458363105703</v>
+      </c>
+      <c r="F65">
+        <v>10.0312234529262</v>
+      </c>
+      <c r="G65">
+        <v>136.69999999999999</v>
+      </c>
+      <c r="H65">
+        <v>145.6</v>
+      </c>
+      <c r="I65">
+        <v>118.9</v>
+      </c>
+      <c r="J65">
+        <v>-0.2</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="0"/>
+        <v>103.21428571428572</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="1"/>
+        <v>109.13312693498452</v>
+      </c>
+      <c r="M65">
+        <v>550584.71877029398</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="2"/>
+        <v>111.30107417133748</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2006</v>
       </c>
@@ -26449,8 +28640,44 @@
       <c r="C66">
         <v>2140</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D66">
+        <v>589.09725018455504</v>
+      </c>
+      <c r="E66">
+        <v>52905.175744968903</v>
+      </c>
+      <c r="F66">
+        <v>9.5544729276578995</v>
+      </c>
+      <c r="G66">
+        <v>141.69999999999999</v>
+      </c>
+      <c r="H66">
+        <v>151.5</v>
+      </c>
+      <c r="I66">
+        <v>122.4</v>
+      </c>
+      <c r="J66">
+        <v>-0.3</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="0"/>
+        <v>103.21428571428572</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="1"/>
+        <v>110.42311661506707</v>
+      </c>
+      <c r="M66">
+        <v>573347.66719402105</v>
+      </c>
+      <c r="N66">
+        <f t="shared" si="2"/>
+        <v>115.90261962745933</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2007</v>
       </c>
@@ -26460,8 +28687,44 @@
       <c r="C67">
         <v>2175</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D67">
+        <v>610.55885964372101</v>
+      </c>
+      <c r="E67">
+        <v>55324.812951322703</v>
+      </c>
+      <c r="F67">
+        <v>9.3916494829341506</v>
+      </c>
+      <c r="G67">
+        <v>143.1</v>
+      </c>
+      <c r="H67">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="I67">
+        <v>123</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="0"/>
+        <v>104.28571428571429</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="1"/>
+        <v>112.22910216718267</v>
+      </c>
+      <c r="M67">
+        <v>596185.21556237596</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="2"/>
+        <v>120.51924551296314</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2008</v>
       </c>
@@ -26471,8 +28734,44 @@
       <c r="C68">
         <v>2219</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D68">
+        <v>636.42535086293003</v>
+      </c>
+      <c r="E68">
+        <v>58406.090941927898</v>
+      </c>
+      <c r="F68">
+        <v>9.5060802628781005</v>
+      </c>
+      <c r="G68">
+        <v>142.5</v>
+      </c>
+      <c r="H68">
+        <v>151.69999999999999</v>
+      </c>
+      <c r="I68">
+        <v>124.4</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="0"/>
+        <v>103.57142857142858</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="1"/>
+        <v>114.49948400412796</v>
+      </c>
+      <c r="M68">
+        <v>611278.21835853998</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="2"/>
+        <v>123.57030626059154</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2009</v>
       </c>
@@ -26482,8 +28781,44 @@
       <c r="C69">
         <v>2266</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D69">
+        <v>656.36130342030003</v>
+      </c>
+      <c r="E69">
+        <v>60993.012103518296</v>
+      </c>
+      <c r="F69">
+        <v>10.1142719884374</v>
+      </c>
+      <c r="G69">
+        <v>144.6</v>
+      </c>
+      <c r="H69">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="I69">
+        <v>126.6</v>
+      </c>
+      <c r="J69">
+        <v>-0.1</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="0"/>
+        <v>106.42857142857143</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="1"/>
+        <v>116.92466460268318</v>
+      </c>
+      <c r="M69">
+        <v>599450.538071346</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="2"/>
+        <v>121.17933267189468</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2010</v>
       </c>
@@ -26493,8 +28828,44 @@
       <c r="C70">
         <v>2284</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D70">
+        <v>664.51213362353496</v>
+      </c>
+      <c r="E70">
+        <v>62396.9637</v>
+      </c>
+      <c r="F70">
+        <v>9.9907855889225008</v>
+      </c>
+      <c r="G70">
+        <v>156.30000000000001</v>
+      </c>
+      <c r="H70">
+        <v>167.1</v>
+      </c>
+      <c r="I70">
+        <v>134.80000000000001</v>
+      </c>
+      <c r="J70">
+        <v>-0.6</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="0"/>
+        <v>106.42857142857143</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="1"/>
+        <v>117.85345717234262</v>
+      </c>
+      <c r="M70">
+        <v>618996.40692477801</v>
+      </c>
+      <c r="N70">
+        <f t="shared" si="2"/>
+        <v>125.1305433118447</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2011</v>
       </c>
@@ -26504,8 +28875,44 @@
       <c r="C71">
         <v>2306</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D71">
+        <v>676.518502987337</v>
+      </c>
+      <c r="E71">
+        <v>64234.603799999997</v>
+      </c>
+      <c r="F71">
+        <v>10.1039309594507</v>
+      </c>
+      <c r="G71">
+        <v>165.3</v>
+      </c>
+      <c r="H71">
+        <v>177.4</v>
+      </c>
+      <c r="I71">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="J71">
+        <v>-0.4</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="0"/>
+        <v>107.5</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="1"/>
+        <v>118.98864809081526</v>
+      </c>
+      <c r="M71">
+        <v>627709.77554362605</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="2"/>
+        <v>126.89195668542077</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2012</v>
       </c>
@@ -26515,8 +28922,44 @@
       <c r="C72">
         <v>2326</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D72">
+        <v>693.204102209604</v>
+      </c>
+      <c r="E72">
+        <v>66521.482199999999</v>
+      </c>
+      <c r="F72">
+        <v>10.335110397685099</v>
+      </c>
+      <c r="G72">
+        <v>168.5</v>
+      </c>
+      <c r="H72">
+        <v>181.3</v>
+      </c>
+      <c r="I72">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="J72">
+        <v>-0.2</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="0"/>
+        <v>108.92857142857142</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="1"/>
+        <v>120.02063983488131</v>
+      </c>
+      <c r="M72">
+        <v>634766.08641963301</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="2"/>
+        <v>128.31839471287014</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2013</v>
       </c>
@@ -26526,8 +28969,44 @@
       <c r="C73">
         <v>2343</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D73">
+        <v>714.44260643006703</v>
+      </c>
+      <c r="E73">
+        <v>69352.476999999999</v>
+      </c>
+      <c r="F73">
+        <v>10.5944455755102</v>
+      </c>
+      <c r="G73">
+        <v>170.4</v>
+      </c>
+      <c r="H73">
+        <v>183.1</v>
+      </c>
+      <c r="I73">
+        <v>144.9</v>
+      </c>
+      <c r="J73">
+        <v>-0.1</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="0"/>
+        <v>110.00000000000001</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="1"/>
+        <v>120.89783281733746</v>
+      </c>
+      <c r="M73">
+        <v>646421.178282368</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="2"/>
+        <v>130.67447943455534</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2014</v>
       </c>
@@ -26537,8 +29016,44 @@
       <c r="C74">
         <v>2361</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D74">
+        <v>723.11033479252796</v>
+      </c>
+      <c r="E74">
+        <v>71055.556299999997</v>
+      </c>
+      <c r="F74">
+        <v>10.6751194116164</v>
+      </c>
+      <c r="G74">
+        <v>169</v>
+      </c>
+      <c r="H74">
+        <v>187.4</v>
+      </c>
+      <c r="I74">
+        <v>129.9</v>
+      </c>
+      <c r="J74">
+        <v>0.1</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="0"/>
+        <v>111.07142857142858</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="1"/>
+        <v>121.82662538699691</v>
+      </c>
+      <c r="M74">
+        <v>662862.40631210397</v>
+      </c>
+      <c r="N74">
+        <f t="shared" si="2"/>
+        <v>133.99808482718694</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>2015</v>
       </c>
@@ -26548,8 +29063,44 @@
       <c r="C75">
         <v>2370</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D75">
+        <v>737.97051501361</v>
+      </c>
+      <c r="E75">
+        <v>73345.968500000003</v>
+      </c>
+      <c r="F75">
+        <v>10.9798305090147</v>
+      </c>
+      <c r="G75">
+        <v>173.3</v>
+      </c>
+      <c r="H75">
+        <v>194.6</v>
+      </c>
+      <c r="I75">
+        <v>127.8</v>
+      </c>
+      <c r="J75">
+        <v>-0.2</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="0"/>
+        <v>112.5</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="1"/>
+        <v>122.29102167182661</v>
+      </c>
+      <c r="M75">
+        <v>672503.76154870098</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="2"/>
+        <v>135.94709132467457</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>2016</v>
       </c>
@@ -26559,8 +29110,44 @@
       <c r="C76">
         <v>2386</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D76">
+        <v>755.73084274554901</v>
+      </c>
+      <c r="E76">
+        <v>75935.877399999998</v>
+      </c>
+      <c r="F76">
+        <v>11.202487927763899</v>
+      </c>
+      <c r="G76">
+        <v>178.5</v>
+      </c>
+      <c r="H76">
+        <v>204</v>
+      </c>
+      <c r="I76">
+        <v>124.1</v>
+      </c>
+      <c r="J76">
+        <v>-0.2</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="0"/>
+        <v>113.92857142857142</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="1"/>
+        <v>123.11661506707947</v>
+      </c>
+      <c r="M76">
+        <v>685359.28335051099</v>
+      </c>
+      <c r="N76">
+        <f t="shared" si="2"/>
+        <v>138.5458437723818</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>2017</v>
       </c>
@@ -26570,8 +29157,44 @@
       <c r="C77">
         <v>2395</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D77">
+        <v>767.74784445359398</v>
+      </c>
+      <c r="E77">
+        <v>77866.583299999998</v>
+      </c>
+      <c r="F77">
+        <v>11.3747162586182</v>
+      </c>
+      <c r="G77">
+        <v>185.3</v>
+      </c>
+      <c r="H77">
+        <v>213.9</v>
+      </c>
+      <c r="I77">
+        <v>124.6</v>
+      </c>
+      <c r="J77">
+        <v>-0.3</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="0"/>
+        <v>113.57142857142857</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="1"/>
+        <v>123.58101135190918</v>
+      </c>
+      <c r="M77">
+        <v>695093.75738472794</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="2"/>
+        <v>140.51367429793868</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2018</v>
       </c>
@@ -26581,8 +29204,44 @@
       <c r="C78">
         <v>2407</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D78">
+        <v>774.88634502024104</v>
+      </c>
+      <c r="E78">
+        <v>79171.642699999997</v>
+      </c>
+      <c r="F78">
+        <v>11.1584548735973</v>
+      </c>
+      <c r="G78">
+        <v>192.83425255256284</v>
+      </c>
+      <c r="H78">
+        <v>221.8</v>
+      </c>
+      <c r="I78">
+        <v>131.1</v>
+      </c>
+      <c r="J78">
+        <v>-0.29999999999999982</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="0"/>
+        <v>113.21428571428571</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="1"/>
+        <v>124.20020639834881</v>
+      </c>
+      <c r="M78">
+        <v>718222.53303125699</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="2"/>
+        <v>145.18917197516453</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2019</v>
       </c>
@@ -26592,8 +29251,44 @@
       <c r="C79">
         <v>2429</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D79">
+        <v>793.81385311422298</v>
+      </c>
+      <c r="E79">
+        <v>81686.112699999998</v>
+      </c>
+      <c r="F79">
+        <v>11.394692749738599</v>
+      </c>
+      <c r="G79">
+        <v>194.4</v>
+      </c>
+      <c r="H79">
+        <v>224.2</v>
+      </c>
+      <c r="I79">
+        <v>131.1</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="0"/>
+        <v>113.92857142857142</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="1"/>
+        <v>125.33539731682146</v>
+      </c>
+      <c r="M79">
+        <v>726233.02622593602</v>
+      </c>
+      <c r="N79">
+        <f t="shared" si="2"/>
+        <v>146.80849860522659</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2020</v>
       </c>
@@ -26603,8 +29298,44 @@
       <c r="C80">
         <v>2449</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D80">
+        <v>805.745927101544</v>
+      </c>
+      <c r="E80">
+        <v>83522.009699999995</v>
+      </c>
+      <c r="F80">
+        <v>11.9896090630887</v>
+      </c>
+      <c r="G80">
+        <v>194.8</v>
+      </c>
+      <c r="H80">
+        <v>224.8</v>
+      </c>
+      <c r="I80">
+        <v>131.19999999999999</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="0"/>
+        <v>115.71428571428572</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="1"/>
+        <v>126.36738906088752</v>
+      </c>
+      <c r="M80">
+        <v>709854.59789991495</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="2"/>
+        <v>143.49758821527635</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2021</v>
       </c>
@@ -26614,8 +29345,44 @@
       <c r="C81">
         <v>2445</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D81">
+        <v>852.99550390080697</v>
+      </c>
+      <c r="E81">
+        <v>89099.258100000006</v>
+      </c>
+      <c r="F81">
+        <v>11.958555935721201</v>
+      </c>
+      <c r="G81">
+        <v>195.3</v>
+      </c>
+      <c r="H81">
+        <v>225.7</v>
+      </c>
+      <c r="I81">
+        <v>130.80000000000001</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="0"/>
+        <v>114.64285714285714</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="1"/>
+        <v>126.16099071207429</v>
+      </c>
+      <c r="M81">
+        <v>753696.83907210804</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="2"/>
+        <v>152.36032699132244</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2022</v>
       </c>
@@ -26625,8 +29392,44 @@
       <c r="C82">
         <v>2468</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D82">
+        <v>871.19961749652396</v>
+      </c>
+      <c r="E82">
+        <v>91759.148499999996</v>
+      </c>
+      <c r="F82">
+        <v>11.599118623235</v>
+      </c>
+      <c r="G82">
+        <v>194.4</v>
+      </c>
+      <c r="H82">
+        <v>224.6</v>
+      </c>
+      <c r="I82">
+        <v>130.30000000000001</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="0"/>
+        <v>112.5</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="1"/>
+        <v>127.34778121775025</v>
+      </c>
+      <c r="M82">
+        <v>780334.76842328196</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="2"/>
+        <v>157.7452024689922</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2023</v>
       </c>
@@ -26636,8 +29439,44 @@
       <c r="C83">
         <v>2510</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D83">
+        <v>880.80922763495698</v>
+      </c>
+      <c r="E83">
+        <v>93952.271999999997</v>
+      </c>
+      <c r="F83">
+        <v>11.6909605770346</v>
+      </c>
+      <c r="G83">
+        <v>202</v>
+      </c>
+      <c r="H83">
+        <v>236.7</v>
+      </c>
+      <c r="I83">
+        <v>129.6</v>
+      </c>
+      <c r="J83">
+        <v>-0.4</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="0"/>
+        <v>112.14285714285714</v>
+      </c>
+      <c r="L83">
+        <f t="shared" si="1"/>
+        <v>129.51496388028895</v>
+      </c>
+      <c r="M83">
+        <v>786776.90694842604</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="2"/>
+        <v>159.04748513933313</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>2024</v>
       </c>
@@ -26646,6 +29485,68 @@
       </c>
       <c r="C84">
         <v>2555</v>
+      </c>
+      <c r="D84">
+        <v>898.57945374721101</v>
+      </c>
+      <c r="E84">
+        <v>97076.374305067206</v>
+      </c>
+      <c r="F84">
+        <v>11.7726930091663</v>
+      </c>
+      <c r="G84">
+        <v>213.9</v>
+      </c>
+      <c r="H84">
+        <v>255.9</v>
+      </c>
+      <c r="I84">
+        <v>128.1</v>
+      </c>
+      <c r="J84">
+        <v>-0.5</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="0"/>
+        <v>112.85714285714286</v>
+      </c>
+      <c r="L84">
+        <f t="shared" si="1"/>
+        <v>131.83694530443756</v>
+      </c>
+      <c r="M84">
+        <v>797715.73105106899</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="2"/>
+        <v>161.25877584771806</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G85">
+        <v>222.9</v>
+      </c>
+      <c r="H85">
+        <v>270.39999999999998</v>
+      </c>
+      <c r="I85">
+        <v>127.4</v>
+      </c>
+      <c r="J85">
+        <v>-0.3</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
